--- a/results/tables/tHRR-I_public_data_results.xlsx
+++ b/results/tables/tHRR-I_public_data_results.xlsx
@@ -2,22 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R3456645ed06442ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prediction performance" sheetId="2" r:id="Ra9a1819e1a8e4725"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prediction comparisons" sheetId="3" r:id="R38a04d218ca04c2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Within-person summary" sheetId="4" r:id="R60ee79dbbb344b11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participant associations" sheetId="5" r:id="R4a7dddb33bed4442"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discretization" sheetId="6" r:id="Re4a9a93251f34870"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repeated splits summary" sheetId="7" r:id="R7c2a7c7c88a34ca9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repeated splits" sheetId="8" r:id="R7fb271d24ab64e97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matching stability" sheetId="9" r:id="R2c26ded132294291"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High RPE balanced" sheetId="10" r:id="Rab67173b90144790"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High RPE participant" sheetId="11" r:id="R973760266989447c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ordinal sensitivity" sheetId="12" r:id="Rc2d294cbd16248d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HRR clipping" sheetId="13" r:id="R4c2d5b5a61db490c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prediction range" sheetId="14" r:id="Rac7fb1e760aa4485"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equal-mean examples" sheetId="15" r:id="R0985bc2b915e4d28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participant anchors" sheetId="16" r:id="R8e71517a106343af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rde40f86ed25a43a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prediction performance" sheetId="2" r:id="R3c612935666c4964"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prediction comparisons" sheetId="3" r:id="Rfa20b8268a2e4269"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Within-person summary" sheetId="4" r:id="Rd43c2d9230364a69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participant associations" sheetId="5" r:id="Ree9b0008790348f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discretization" sheetId="6" r:id="R30725bc87e174aa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repeated splits summary" sheetId="7" r:id="R83932f81b2ac4fbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repeated splits" sheetId="8" r:id="R197199db3bb14607"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matching stability" sheetId="9" r:id="R7164591f809441e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High RPE balanced" sheetId="10" r:id="R76245abdc79e4006"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High RPE participant" sheetId="11" r:id="Rf7dcd64dedeb4e59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ordinal sensitivity" sheetId="12" r:id="R9e576224f9cf491c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HRR clipping" sheetId="13" r:id="R2d862d0bb17c40d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prediction range" sheetId="14" r:id="R31b3e2b568994afe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equal-mean examples" sheetId="15" r:id="R7d379f069b0b462b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw signal anchors" sheetId="16" r:id="R0447b8908c6e4530"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matching model performance" sheetId="17" r:id="R24b5e2b4937c43c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weight profile" sheetId="18" r:id="R9f612ae7e99144c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participant anchors" sheetId="19" r:id="R957c16fa2eca4c87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selection aware" sheetId="20" r:id="R6847d934b20d4aff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matching confidence" sheetId="21" r:id="R5d8f46733fde4d86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lambda heterogeneity" sheetId="22" r:id="Rcb48ec60a0b04dd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEE repeated measures" sheetId="23" r:id="Rf640f6b88e0f4fbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEE agreement" sheetId="24" r:id="Rbf2d5df6188d4264"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEE agreement intervals" sheetId="25" r:id="Rc2e075705c184385"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEE synchronization" sheetId="26" r:id="Rf2a81f0554064dc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Malaga endpoint sensitivity" sheetId="27" r:id="R52a2202dcfee426a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Malaga anchor sensitivity" sheetId="28" r:id="Re1b0523768b74030"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -28,10 +40,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="164" formatCode="0.0000"/>
+    <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -45,8 +58,25 @@
       <x:b/>
       <x:color rgb="FF007C91"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color theme="1"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF007C91"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -63,14 +93,64 @@
         <x:fgColor rgb="FFEAF3F6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1E3F66"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3F6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1E3F66"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3F6"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="4">
     <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF1E3F66"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF1E3F66"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF1E3F66"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FF1E3F66"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF1E3F66"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF1E3F66"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF1E3F66"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF1E3F66"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="66">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,6 +178,138 @@
     </x:xf>
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="164" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="164" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -390,116 +602,128 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="26" customWidth="1"/>
-    <x:col min="2" max="2" width="95" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="92" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Item</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Value</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Workbook purpose</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Auditable tables supporting the revised tHRR-I PMData manuscript</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Independent unit</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Participant; sessions are repeated observations</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Primary comparison</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Participant-balanced held-out MAE: ten-bin tHRR-I versus linear decile score</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Primary result</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MAE difference -0.0965 RPE units; reviewer-revision conditional 95% CI -0.1637 to -0.0327</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Development estimate</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ten-bin lambda=6.2; lock before independent validation</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Uncertainty</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cluster-bootstrap intervals condition on realized predictions and exclude formula-family selection</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Software</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Python 3.12.13; pandas 2.2.3; NumPy 2.3.5; openpyxl 3.1.5</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Raw data</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PMData is not redistributed; configure PMDATA_ROOT to a licensed local copy</x:t>
-        </x:is>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="54" t="str">
+        <x:v>Item</x:v>
+      </x:c>
+      <x:c r="B1" s="56" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="65" t="str">
+        <x:v>Workbook purpose</x:v>
+      </x:c>
+      <x:c r="B2" s="64" t="str">
+        <x:v>Auditable PMData, WEEE, and Malaga tables supporting the revised tHRR-I manuscript</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="48" t="str">
+        <x:v>Independent unit</x:v>
+      </x:c>
+      <x:c r="B3" s="41" t="str">
+        <x:v>Participant; sessions, stages, and tests are repeated observations</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="65" t="str">
+        <x:v>Development status</x:v>
+      </x:c>
+      <x:c r="B4" s="64" t="str">
+        <x:v>Exploratory PMData method development; principal comparison was not preregistered</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="48" t="str">
+        <x:v>Selection-aware result</x:v>
+      </x:c>
+      <x:c r="B5" s="41" t="str">
+        <x:v>Outer LOPO reselected family and parameter: ΔMAE -0.094 RPE units (95% CI -0.161 to -0.031)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="65" t="str">
+        <x:v>Matching negative control</x:v>
+      </x:c>
+      <x:c r="B6" s="64" t="str">
+        <x:v>Strict tier retained 203 sessions; 5,000 circular within-participant RPE permutations gave P=0.00020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="48" t="str">
+        <x:v>Locked external parameter</x:v>
+      </x:c>
+      <x:c r="B7" s="41" t="str">
+        <x:v>Ten-bin tHRR-I, λ=6.2; fixed before external outcome inspection</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="65" t="str">
+        <x:v>WEEE repeated measures</x:v>
+      </x:c>
+      <x:c r="B8" s="64" t="str">
+        <x:v>Within-participant r: tHRR-I 0.861 vs mean HRR 0.855; difference 0.006 (-0.008 to 0.027)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="48" t="str">
+        <x:v>WEEE incremental prediction</x:v>
+      </x:c>
+      <x:c r="B9" s="41" t="str">
+        <x:v>Adding Δtilt: ΔMAE 0.024 mL·kg⁻¹·min⁻¹ (-0.115 to 0.170)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="65" t="str">
+        <x:v>Zephyr agreement</x:v>
+      </x:c>
+      <x:c r="B10" s="64" t="str">
+        <x:v>tHRR-I ICC(A,1) 0.854 (0.667 to 0.952); limits of agreement -0.257 to 0.205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="48" t="str">
+        <x:v>Malaga incremental prediction</x:v>
+      </x:c>
+      <x:c r="B11" s="41" t="str">
+        <x:v>Primary 180-s endpoint ΔMAE 0.009 mL (-1.234 to 1.276); no stable sensitivity-analysis benefit</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="65" t="str">
+        <x:v>Practical interpretation</x:v>
+      </x:c>
+      <x:c r="B12" s="64" t="str">
+        <x:v>Candidate retrospective session-review descriptor; not a prescription, alert, or clinical measure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="48" t="str">
+        <x:v>Uncertainty</x:v>
+      </x:c>
+      <x:c r="B13" s="41" t="str">
+        <x:v>Participant-cluster intervals; formula-invention optimism remains in PMData</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="65" t="str">
+        <x:v>Raw data</x:v>
+      </x:c>
+      <x:c r="B14" s="64" t="str">
+        <x:v>Third-party raw data are not redistributed; see source manifests and repository access terms</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="48" t="str">
+        <x:v>Software</x:v>
+      </x:c>
+      <x:c r="B15" s="41" t="str">
+        <x:v>Python 3.12.13; pandas 2.2.3; NumPy 2.3.5; openpyxl 3.1.5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1535,6 +1759,1027 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="12" customWidth="1"/>
+    <x:col min="2" max="2" width="14" customWidth="1"/>
+    <x:col min="3" max="3" width="18" customWidth="1"/>
+    <x:col min="4" max="4" width="21" customWidth="1"/>
+    <x:col min="5" max="5" width="17" customWidth="1"/>
+    <x:col min="6" max="6" width="17" customWidth="1"/>
+    <x:col min="7" max="7" width="33" customWidth="1"/>
+    <x:col min="8" max="8" width="33" customWidth="1"/>
+    <x:col min="9" max="9" width="34" customWidth="1"/>
+    <x:col min="10" max="10" width="21" customWidth="1"/>
+    <x:col min="11" max="11" width="21" customWidth="1"/>
+    <x:col min="12" max="12" width="23" customWidth="1"/>
+    <x:col min="13" max="13" width="34" customWidth="1"/>
+    <x:col min="14" max="14" width="34" customWidth="1"/>
+    <x:col min="15" max="15" width="29" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sessions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">participants</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">full_data_lambda</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">outer_lambda_median</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">outer_lambda_q1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">outer_lambda_q3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">participant_balanced_mae_tilted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">participant_balanced_mae_linear</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">mae_difference_tilted_minus_linear</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">conditional_ci_low</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">conditional_ci_high</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">participants_with_rho</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">median_within_participant_rho_tilted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">median_within_participant_rho_linear</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">variant</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="6" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="n">
+        <x:v>8.9</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="n">
+        <x:v>9.300000000000001</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="n">
+        <x:v>1.205543813468112</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="n">
+        <x:v>1.302046419535711</x:v>
+      </x:c>
+      <x:c r="I2" s="7" t="n">
+        <x:v>-0.0965026060675999</x:v>
+      </x:c>
+      <x:c r="J2" s="7" t="n">
+        <x:v>-0.1628101254886511</x:v>
+      </x:c>
+      <x:c r="K2" s="7" t="n">
+        <x:v>-0.0287018079568021</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M2" s="7" t="n">
+        <x:v>0.6660845595943223</x:v>
+      </x:c>
+      <x:c r="N2" s="7" t="n">
+        <x:v>0.422008346476664</x:v>
+      </x:c>
+      <x:c r="O2" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">baseline_rebuilt</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="8" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="n">
+        <x:v>9.300000000000001</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="F3" s="9" t="n">
+        <x:v>9.949999999999999</x:v>
+      </x:c>
+      <x:c r="G3" s="9" t="n">
+        <x:v>1.203278737921187</x:v>
+      </x:c>
+      <x:c r="H3" s="9" t="n">
+        <x:v>1.302021643304362</x:v>
+      </x:c>
+      <x:c r="I3" s="9" t="n">
+        <x:v>-0.0987429053831753</x:v>
+      </x:c>
+      <x:c r="J3" s="9" t="n">
+        <x:v>-0.1687624082489788</x:v>
+      </x:c>
+      <x:c r="K3" s="9" t="n">
+        <x:v>-0.0306978517707119</x:v>
+      </x:c>
+      <x:c r="L3" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M3" s="9" t="n">
+        <x:v>0.668582376692801</x:v>
+      </x:c>
+      <x:c r="N3" s="9" t="n">
+        <x:v>0.422008346476664</x:v>
+      </x:c>
+      <x:c r="O3" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upper_0.5pct_bpm_winsorized</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="n">
+        <x:v>8.1</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="n">
+        <x:v>9.949999999999999</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="n">
+        <x:v>1.208329711293426</x:v>
+      </x:c>
+      <x:c r="H4" s="7" t="n">
+        <x:v>1.301993705737812</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="n">
+        <x:v>-0.0936639944443866</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="n">
+        <x:v>-0.1583199324943171</x:v>
+      </x:c>
+      <x:c r="K4" s="7" t="n">
+        <x:v>-0.02838212571159</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M4" s="7" t="n">
+        <x:v>0.668582376692801</x:v>
+      </x:c>
+      <x:c r="N4" s="7" t="n">
+        <x:v>0.4176848756664353</x:v>
+      </x:c>
+      <x:c r="O4" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upper_1pct_bpm_winsorized</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="8" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="n">
+        <x:v>8.9</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="n">
+        <x:v>9.300000000000001</x:v>
+      </x:c>
+      <x:c r="G5" s="9" t="n">
+        <x:v>1.205543813468112</x:v>
+      </x:c>
+      <x:c r="H5" s="9" t="n">
+        <x:v>1.302046419535711</x:v>
+      </x:c>
+      <x:c r="I5" s="9" t="n">
+        <x:v>-0.0965026060675999</x:v>
+      </x:c>
+      <x:c r="J5" s="9" t="n">
+        <x:v>-0.1612657845459938</x:v>
+      </x:c>
+      <x:c r="K5" s="9" t="n">
+        <x:v>-0.0300950979669478</x:v>
+      </x:c>
+      <x:c r="L5" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M5" s="9" t="n">
+        <x:v>0.6660845595943223</x:v>
+      </x:c>
+      <x:c r="N5" s="9" t="n">
+        <x:v>0.422008346476664</x:v>
+      </x:c>
+      <x:c r="O5" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hrr_capped_at_0.95</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="6" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="D6" s="7" t="n">
+        <x:v>8.9</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="F6" s="7" t="n">
+        <x:v>9.300000000000001</x:v>
+      </x:c>
+      <x:c r="G6" s="7" t="n">
+        <x:v>1.205539081066618</x:v>
+      </x:c>
+      <x:c r="H6" s="7" t="n">
+        <x:v>1.302061841736956</x:v>
+      </x:c>
+      <x:c r="I6" s="7" t="n">
+        <x:v>-0.0965227606703382</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="n">
+        <x:v>-0.1646552999236557</x:v>
+      </x:c>
+      <x:c r="K6" s="7" t="n">
+        <x:v>-0.0329003174131236</x:v>
+      </x:c>
+      <x:c r="L6" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M6" s="7" t="n">
+        <x:v>0.6660845595943223</x:v>
+      </x:c>
+      <x:c r="N6" s="7" t="n">
+        <x:v>0.422008346476664</x:v>
+      </x:c>
+      <x:c r="O6" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">gap_cap_15_seconds</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="n"/>
+      <x:c r="D7" s="8" t="n"/>
+      <x:c r="E7" s="8" t="n"/>
+      <x:c r="F7" s="8" t="n"/>
+      <x:c r="G7" s="8" t="n"/>
+      <x:c r="H7" s="8" t="n"/>
+      <x:c r="I7" s="8" t="n"/>
+      <x:c r="J7" s="8" t="n"/>
+      <x:c r="K7" s="8" t="n"/>
+      <x:c r="L7" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="8" t="n"/>
+      <x:c r="N7" s="8" t="n"/>
+      <x:c r="O7" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">confidence_3_only</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="6" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="n">
+        <x:v>6.9</x:v>
+      </x:c>
+      <x:c r="D8" s="7" t="n">
+        <x:v>7.9</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="n">
+        <x:v>6.9</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G8" s="7" t="n">
+        <x:v>1.226434859287665</x:v>
+      </x:c>
+      <x:c r="H8" s="7" t="n">
+        <x:v>1.309859280816649</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="n">
+        <x:v>-0.08342442152898311</x:v>
+      </x:c>
+      <x:c r="J8" s="7" t="n">
+        <x:v>-0.1460864674778212</x:v>
+      </x:c>
+      <x:c r="K8" s="7" t="n">
+        <x:v>-0.019483319679797</x:v>
+      </x:c>
+      <x:c r="L8" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M8" s="7" t="n">
+        <x:v>0.642771600008521</x:v>
+      </x:c>
+      <x:c r="N8" s="7" t="n">
+        <x:v>0.4120455659139632</x:v>
+      </x:c>
+      <x:c r="O8" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hrmax_plus_5_bpm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="8" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B9" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="n">
+        <x:v>6.8</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="n">
+        <x:v>7.4</x:v>
+      </x:c>
+      <x:c r="E9" s="9" t="n">
+        <x:v>6.8</x:v>
+      </x:c>
+      <x:c r="F9" s="9" t="n">
+        <x:v>8.300000000000001</x:v>
+      </x:c>
+      <x:c r="G9" s="9" t="n">
+        <x:v>1.208329878231355</x:v>
+      </x:c>
+      <x:c r="H9" s="9" t="n">
+        <x:v>1.306356239379363</x:v>
+      </x:c>
+      <x:c r="I9" s="9" t="n">
+        <x:v>-0.0980263611480082</x:v>
+      </x:c>
+      <x:c r="J9" s="9" t="n">
+        <x:v>-0.1549878709566982</x:v>
+      </x:c>
+      <x:c r="K9" s="9" t="n">
+        <x:v>-0.0404967252985573</x:v>
+      </x:c>
+      <x:c r="L9" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M9" s="9" t="n">
+        <x:v>0.6191811051895554</x:v>
+      </x:c>
+      <x:c r="N9" s="9" t="n">
+        <x:v>0.4466333323957922</x:v>
+      </x:c>
+      <x:c r="O9" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hrmax_minus_5_bpm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="6" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="7" t="n">
+        <x:v>5.8</x:v>
+      </x:c>
+      <x:c r="D10" s="7" t="n">
+        <x:v>8.5</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="n">
+        <x:v>5.8</x:v>
+      </x:c>
+      <x:c r="F10" s="7" t="n">
+        <x:v>8.699999999999999</x:v>
+      </x:c>
+      <x:c r="G10" s="7" t="n">
+        <x:v>1.205515369483684</x:v>
+      </x:c>
+      <x:c r="H10" s="7" t="n">
+        <x:v>1.301211817754223</x:v>
+      </x:c>
+      <x:c r="I10" s="7" t="n">
+        <x:v>-0.09569644827053921</x:v>
+      </x:c>
+      <x:c r="J10" s="7" t="n">
+        <x:v>-0.1621202595155443</x:v>
+      </x:c>
+      <x:c r="K10" s="7" t="n">
+        <x:v>-0.0291501555710903</x:v>
+      </x:c>
+      <x:c r="L10" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M10" s="7" t="n">
+        <x:v>0.6980011114082169</x:v>
+      </x:c>
+      <x:c r="N10" s="7" t="n">
+        <x:v>0.4253919323281472</x:v>
+      </x:c>
+      <x:c r="O10" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hrrest_plus_3_bpm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="8" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="n">
+        <x:v>7.2</x:v>
+      </x:c>
+      <x:c r="E11" s="9" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="F11" s="9" t="n">
+        <x:v>8.699999999999999</x:v>
+      </x:c>
+      <x:c r="G11" s="9" t="n">
+        <x:v>1.21473456763475</x:v>
+      </x:c>
+      <x:c r="H11" s="9" t="n">
+        <x:v>1.30053936613896</x:v>
+      </x:c>
+      <x:c r="I11" s="9" t="n">
+        <x:v>-0.0858047985042102</x:v>
+      </x:c>
+      <x:c r="J11" s="9" t="n">
+        <x:v>-0.1515737286832604</x:v>
+      </x:c>
+      <x:c r="K11" s="9" t="n">
+        <x:v>-0.0230765002339975</x:v>
+      </x:c>
+      <x:c r="L11" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M11" s="9" t="n">
+        <x:v>0.6597012492315434</x:v>
+      </x:c>
+      <x:c r="N11" s="9" t="n">
+        <x:v>0.4208804845261695</x:v>
+      </x:c>
+      <x:c r="O11" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hrrest_minus_3_bpm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="6" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="7" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="D12" s="7" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="F12" s="7" t="n">
+        <x:v>9.1</x:v>
+      </x:c>
+      <x:c r="G12" s="7" t="n">
+        <x:v>1.374436584137854</x:v>
+      </x:c>
+      <x:c r="H12" s="7" t="n">
+        <x:v>1.406398053321581</x:v>
+      </x:c>
+      <x:c r="I12" s="7" t="n">
+        <x:v>-0.0319614691837272</x:v>
+      </x:c>
+      <x:c r="J12" s="7" t="n">
+        <x:v>-0.0836079792391399</x:v>
+      </x:c>
+      <x:c r="K12" s="7" t="n">
+        <x:v>0.0258185994710104</x:v>
+      </x:c>
+      <x:c r="L12" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M12" s="7" t="n">
+        <x:v>0.6438817409411781</x:v>
+      </x:c>
+      <x:c r="N12" s="7" t="n">
+        <x:v>0.422008346476664</x:v>
+      </x:c>
+      <x:c r="O12" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">tanaka_hrmax_for_all</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" customWidth="1"/>
+    <x:col min="2" max="2" width="14" customWidth="1"/>
+    <x:col min="3" max="3" width="18" customWidth="1"/>
+    <x:col min="4" max="4" width="21" customWidth="1"/>
+    <x:col min="5" max="5" width="17" customWidth="1"/>
+    <x:col min="6" max="6" width="17" customWidth="1"/>
+    <x:col min="7" max="7" width="33" customWidth="1"/>
+    <x:col min="8" max="8" width="33" customWidth="1"/>
+    <x:col min="9" max="9" width="34" customWidth="1"/>
+    <x:col min="10" max="10" width="21" customWidth="1"/>
+    <x:col min="11" max="11" width="21" customWidth="1"/>
+    <x:col min="12" max="12" width="23" customWidth="1"/>
+    <x:col min="13" max="13" width="34" customWidth="1"/>
+    <x:col min="14" max="14" width="34" customWidth="1"/>
+    <x:col min="15" max="15" width="31" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sessions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">participants</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">full_data_lambda</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">outer_lambda_median</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">outer_lambda_q1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">outer_lambda_q3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">participant_balanced_mae_tilted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">participant_balanced_mae_linear</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">mae_difference_tilted_minus_linear</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">conditional_ci_low</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">conditional_ci_high</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">participants_with_rho</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">median_within_participant_rho_tilted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">median_within_participant_rho_linear</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">matching_rule</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="6" t="n">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="n">
+        <x:v>1.220932522220175</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="n">
+        <x:v>1.309460243339419</x:v>
+      </x:c>
+      <x:c r="I2" s="7" t="n">
+        <x:v>-0.0885277211192438</x:v>
+      </x:c>
+      <x:c r="J2" s="7" t="n">
+        <x:v>-0.1493376581086613</x:v>
+      </x:c>
+      <x:c r="K2" s="7" t="n">
+        <x:v>-0.0292524134496347</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M2" s="7" t="n">
+        <x:v>0.6752839811119365</x:v>
+      </x:c>
+      <x:c r="N2" s="7" t="n">
+        <x:v>0.4476936711211663</x:v>
+      </x:c>
+      <x:c r="O2" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delay_15_90_min</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="8" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="n">
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="F3" s="9" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G3" s="9" t="n">
+        <x:v>1.206703357353628</x:v>
+      </x:c>
+      <x:c r="H3" s="9" t="n">
+        <x:v>1.290064937349276</x:v>
+      </x:c>
+      <x:c r="I3" s="9" t="n">
+        <x:v>-0.08336157999564781</x:v>
+      </x:c>
+      <x:c r="J3" s="9" t="n">
+        <x:v>-0.1506577294686418</x:v>
+      </x:c>
+      <x:c r="K3" s="9" t="n">
+        <x:v>-0.0243780808066615</x:v>
+      </x:c>
+      <x:c r="L3" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M3" s="9" t="n">
+        <x:v>0.6660845595943223</x:v>
+      </x:c>
+      <x:c r="N3" s="9" t="n">
+        <x:v>0.3934910986988711</x:v>
+      </x:c>
+      <x:c r="O3" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delay_30_120_min</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="n">
+        <x:v>8.699999999999999</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="n">
+        <x:v>1.212190298192195</x:v>
+      </x:c>
+      <x:c r="H4" s="7" t="n">
+        <x:v>1.280152896175798</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="n">
+        <x:v>-0.0679625979836027</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="n">
+        <x:v>-0.1297910860547085</x:v>
+      </x:c>
+      <x:c r="K4" s="7" t="n">
+        <x:v>-0.0088527335740492</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M4" s="7" t="n">
+        <x:v>0.6515501692769458</x:v>
+      </x:c>
+      <x:c r="N4" s="7" t="n">
+        <x:v>0.4228603470821925</x:v>
+      </x:c>
+      <x:c r="O4" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">duration_difference_le_10_min</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="8" t="n">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="n">
+        <x:v>9.300000000000001</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="n">
+        <x:v>9.300000000000001</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="n">
+        <x:v>9.300000000000001</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="n">
+        <x:v>11.9</x:v>
+      </x:c>
+      <x:c r="G5" s="9" t="n">
+        <x:v>1.202403703639696</x:v>
+      </x:c>
+      <x:c r="H5" s="9" t="n">
+        <x:v>1.297049006588182</x:v>
+      </x:c>
+      <x:c r="I5" s="9" t="n">
+        <x:v>-0.09464530294848621</x:v>
+      </x:c>
+      <x:c r="J5" s="9" t="n">
+        <x:v>-0.1649490314359964</x:v>
+      </x:c>
+      <x:c r="K5" s="9" t="n">
+        <x:v>-0.0286409279769903</x:v>
+      </x:c>
+      <x:c r="L5" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M5" s="9" t="n">
+        <x:v>0.6117962277544905</x:v>
+      </x:c>
+      <x:c r="N5" s="9" t="n">
+        <x:v>0.4112999430726169</x:v>
+      </x:c>
+      <x:c r="O5" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delay_priority_cost</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="6" t="n">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="n">
+        <x:v>9.300000000000001</x:v>
+      </x:c>
+      <x:c r="D6" s="7" t="n">
+        <x:v>9.300000000000001</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="n">
+        <x:v>9.300000000000001</x:v>
+      </x:c>
+      <x:c r="F6" s="7" t="n">
+        <x:v>11.9</x:v>
+      </x:c>
+      <x:c r="G6" s="7" t="n">
+        <x:v>1.202403703639696</x:v>
+      </x:c>
+      <x:c r="H6" s="7" t="n">
+        <x:v>1.297049006588182</x:v>
+      </x:c>
+      <x:c r="I6" s="7" t="n">
+        <x:v>-0.09464530294848621</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="n">
+        <x:v>-0.1632723352163422</x:v>
+      </x:c>
+      <x:c r="K6" s="7" t="n">
+        <x:v>-0.0256286580437887</x:v>
+      </x:c>
+      <x:c r="L6" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M6" s="7" t="n">
+        <x:v>0.6117962277544905</x:v>
+      </x:c>
+      <x:c r="N6" s="7" t="n">
+        <x:v>0.4112999430726169</x:v>
+      </x:c>
+      <x:c r="O6" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">duration_priority_cost</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" customWidth="1"/>
+    <x:col min="2" max="2" width="28" customWidth="1"/>
+    <x:col min="3" max="3" width="27" customWidth="1"/>
+    <x:col min="4" max="4" width="34" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">full_data_lambda</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">adjacent_decile_multiplier</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">weight_ratio_0.95_vs_0.05</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">interpretation</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="n">
+        <x:v>1.858928041846342</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="n">
+        <x:v>265.0716057862269</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Relative exponential weight before normalization; the final index remains bounded in [0,1].</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="13" customWidth="1"/>
     <x:col min="2" max="2" width="12" customWidth="1"/>
     <x:col min="3" max="3" width="12" customWidth="1"/>
@@ -2484,6 +3729,4474 @@
       </x:c>
       <x:c r="K8" s="7" t="n">
         <x:v>0.1512468272900815</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="58" hidden="0" customHeight="1">
+      <x:c r="A1" s="54" t="str">
+        <x:v>held_out_participant</x:v>
+      </x:c>
+      <x:c r="B1" s="55" t="str">
+        <x:v>selected_family</x:v>
+      </x:c>
+      <x:c r="C1" s="55" t="str">
+        <x:v>selected_parameter</x:v>
+      </x:c>
+      <x:c r="D1" s="56" t="str">
+        <x:v>training_objective_median_rho</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="57" t="str">
+        <x:v>p01</x:v>
+      </x:c>
+      <x:c r="B2" s="57" t="str">
+        <x:v>tilted_hrr</x:v>
+      </x:c>
+      <x:c r="C2" s="58" t="str">
+        <x:v>9.3</x:v>
+      </x:c>
+      <x:c r="D2" s="58" t="str">
+        <x:v>0.7349656783964826</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="20" t="str">
+        <x:v>p02</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>tilted_hrr</x:v>
+      </x:c>
+      <x:c r="C3" s="37" t="str">
+        <x:v>9.3</x:v>
+      </x:c>
+      <x:c r="D3" s="37" t="str">
+        <x:v>0.7349656783964826</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="57" t="str">
+        <x:v>p03</x:v>
+      </x:c>
+      <x:c r="B4" s="57" t="str">
+        <x:v>tilted_hrr</x:v>
+      </x:c>
+      <x:c r="C4" s="58" t="str">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="D4" s="58" t="str">
+        <x:v>0.7043844217709958</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="20" t="str">
+        <x:v>p04</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>tilted_hrr</x:v>
+      </x:c>
+      <x:c r="C5" s="37" t="str">
+        <x:v>8.9</x:v>
+      </x:c>
+      <x:c r="D5" s="37" t="str">
+        <x:v>0.6500319973234372</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="57" t="str">
+        <x:v>p05</x:v>
+      </x:c>
+      <x:c r="B6" s="57" t="str">
+        <x:v>tilted_hrr</x:v>
+      </x:c>
+      <x:c r="C6" s="58" t="str">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="D6" s="58" t="str">
+        <x:v>0.7043844217709958</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="20" t="str">
+        <x:v>p06</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>tilted_hrr</x:v>
+      </x:c>
+      <x:c r="C7" s="37" t="str">
+        <x:v>9.4</x:v>
+      </x:c>
+      <x:c r="D7" s="37" t="str">
+        <x:v>0.7116001667432428</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="57" t="str">
+        <x:v>p07</x:v>
+      </x:c>
+      <x:c r="B8" s="57" t="str">
+        <x:v>tilted_hrr</x:v>
+      </x:c>
+      <x:c r="C8" s="58" t="str">
+        <x:v>8.9</x:v>
+      </x:c>
+      <x:c r="D8" s="58" t="str">
+        <x:v>0.6500319973234372</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="20" t="str">
+        <x:v>p08</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>tilted_hrr</x:v>
+      </x:c>
+      <x:c r="C9" s="37" t="str">
+        <x:v>9.3</x:v>
+      </x:c>
+      <x:c r="D9" s="37" t="str">
+        <x:v>0.7349656783964826</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="57" t="str">
+        <x:v>p09</x:v>
+      </x:c>
+      <x:c r="B10" s="57" t="str">
+        <x:v>tilted_hrr</x:v>
+      </x:c>
+      <x:c r="C10" s="58" t="str">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="D10" s="58" t="str">
+        <x:v>0.7043844217709958</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="20" t="str">
+        <x:v>p10</x:v>
+      </x:c>
+      <x:c r="B11" s="20" t="str">
+        <x:v>tilted_hrr</x:v>
+      </x:c>
+      <x:c r="C11" s="37" t="str">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="D11" s="37" t="str">
+        <x:v>0.7043844217709958</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="57" t="str">
+        <x:v>p11</x:v>
+      </x:c>
+      <x:c r="B12" s="57" t="str">
+        <x:v>power_hrr</x:v>
+      </x:c>
+      <x:c r="C12" s="58" t="str">
+        <x:v>12.0</x:v>
+      </x:c>
+      <x:c r="D12" s="58" t="str">
+        <x:v>0.6574704989688218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="20" t="str">
+        <x:v>p12</x:v>
+      </x:c>
+      <x:c r="B13" s="20" t="str">
+        <x:v>tilted_hrr</x:v>
+      </x:c>
+      <x:c r="C13" s="37" t="str">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="D13" s="37" t="str">
+        <x:v>0.7043844217709958</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="57" t="str">
+        <x:v>p13</x:v>
+      </x:c>
+      <x:c r="B14" s="57" t="str">
+        <x:v>tilted_hrr</x:v>
+      </x:c>
+      <x:c r="C14" s="58" t="str">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="D14" s="58" t="str">
+        <x:v>0.7043844217709958</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="20" t="str">
+        <x:v>p14</x:v>
+      </x:c>
+      <x:c r="B15" s="20" t="str">
+        <x:v>tilted_hrr</x:v>
+      </x:c>
+      <x:c r="C15" s="37" t="str">
+        <x:v>8.9</x:v>
+      </x:c>
+      <x:c r="D15" s="37" t="str">
+        <x:v>0.6500319973234372</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="57" t="str">
+        <x:v>p15</x:v>
+      </x:c>
+      <x:c r="B16" s="57" t="str">
+        <x:v>tilted_hrr</x:v>
+      </x:c>
+      <x:c r="C16" s="58" t="str">
+        <x:v>9.3</x:v>
+      </x:c>
+      <x:c r="D16" s="58" t="str">
+        <x:v>0.7349656783964826</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="58" hidden="0" customHeight="1">
+      <x:c r="A1" s="54" t="str">
+        <x:v>matching_tier</x:v>
+      </x:c>
+      <x:c r="B1" s="55" t="str">
+        <x:v>sessions</x:v>
+      </x:c>
+      <x:c r="C1" s="55" t="str">
+        <x:v>participants</x:v>
+      </x:c>
+      <x:c r="D1" s="55" t="str">
+        <x:v>median_report_delay_min</x:v>
+      </x:c>
+      <x:c r="E1" s="56" t="str">
+        <x:v>median_duration_difference_min</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="57" t="str">
+        <x:v>standard</x:v>
+      </x:c>
+      <x:c r="B2" s="59" t="str">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C2" s="59" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D2" s="58" t="str">
+        <x:v>67.06983333333334</x:v>
+      </x:c>
+      <x:c r="E2" s="58" t="str">
+        <x:v>12.274999999999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="20" t="str">
+        <x:v>strict</x:v>
+      </x:c>
+      <x:c r="B3" s="39" t="str">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C3" s="39" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D3" s="37" t="str">
+        <x:v>60.44063333333334</x:v>
+      </x:c>
+      <x:c r="E3" s="37" t="str">
+        <x:v>3.049999999999997</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="58" hidden="0" customHeight="1">
+      <x:c r="A1" s="54" t="str">
+        <x:v>stratum</x:v>
+      </x:c>
+      <x:c r="B1" s="55" t="str">
+        <x:v>sessions</x:v>
+      </x:c>
+      <x:c r="C1" s="55" t="str">
+        <x:v>eligible_participants</x:v>
+      </x:c>
+      <x:c r="D1" s="56" t="str">
+        <x:v>selected_lambda</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="57" t="str">
+        <x:v>all</x:v>
+      </x:c>
+      <x:c r="B2" s="59" t="str">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C2" s="59" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D2" s="58" t="str">
+        <x:v>6.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="20" t="str">
+        <x:v>treadmill</x:v>
+      </x:c>
+      <x:c r="B3" s="39" t="str">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C3" s="39" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="37" t="str">
+        <x:v>7.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="57" t="str">
+        <x:v>run</x:v>
+      </x:c>
+      <x:c r="B4" s="59" t="str">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C4" s="59" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D4" s="58" t="str">
+        <x:v>1.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="20" t="str">
+        <x:v>male</x:v>
+      </x:c>
+      <x:c r="B5" s="39" t="str">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C5" s="39" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" s="37" t="str">
+        <x:v>13.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="57" t="str">
+        <x:v>female</x:v>
+      </x:c>
+      <x:c r="B6" s="59" t="str">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C6" s="59" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="58" t="str">
+        <x:v>7.5</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="58" hidden="0" customHeight="1">
+      <x:c r="A1" s="54" t="str">
+        <x:v>scale</x:v>
+      </x:c>
+      <x:c r="B1" s="55" t="str">
+        <x:v>association</x:v>
+      </x:c>
+      <x:c r="C1" s="55" t="str">
+        <x:v>estimate</x:v>
+      </x:c>
+      <x:c r="D1" s="55" t="str">
+        <x:v>ci_low</x:v>
+      </x:c>
+      <x:c r="E1" s="56" t="str">
+        <x:v>ci_high</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="57" t="str">
+        <x:v>pooled_spearman</x:v>
+      </x:c>
+      <x:c r="B2" s="57" t="str">
+        <x:v>mean_hrr</x:v>
+      </x:c>
+      <x:c r="C2" s="58" t="str">
+        <x:v>0.7571638887428361</x:v>
+      </x:c>
+      <x:c r="D2" s="58" t="str">
+        <x:v>0.6169282698334398</x:v>
+      </x:c>
+      <x:c r="E2" s="58" t="str">
+        <x:v>0.8684976463987942</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="20" t="str">
+        <x:v>pooled_spearman</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>thrr_i</x:v>
+      </x:c>
+      <x:c r="C3" s="37" t="str">
+        <x:v>0.7821457649396947</x:v>
+      </x:c>
+      <x:c r="D3" s="37" t="str">
+        <x:v>0.6595211073699645</x:v>
+      </x:c>
+      <x:c r="E3" s="37" t="str">
+        <x:v>0.879564959886032</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="57" t="str">
+        <x:v>pooled_spearman</x:v>
+      </x:c>
+      <x:c r="B4" s="57" t="str">
+        <x:v>delta_tilt</x:v>
+      </x:c>
+      <x:c r="C4" s="58" t="str">
+        <x:v>0.4569377990430622</x:v>
+      </x:c>
+      <x:c r="D4" s="58" t="str">
+        <x:v>0.23693580644062867</x:v>
+      </x:c>
+      <x:c r="E4" s="58" t="str">
+        <x:v>0.6362374859015748</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="20" t="str">
+        <x:v>pooled_spearman</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>thrr_i_minus_mean_hrr</x:v>
+      </x:c>
+      <x:c r="C5" s="37" t="str">
+        <x:v>0.024981876196858543</x:v>
+      </x:c>
+      <x:c r="D5" s="37" t="str">
+        <x:v>-0.004001362290770524</x:v>
+      </x:c>
+      <x:c r="E5" s="37" t="str">
+        <x:v>0.05695155000042751</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="57" t="str">
+        <x:v>within_participant_pearson</x:v>
+      </x:c>
+      <x:c r="B6" s="57" t="str">
+        <x:v>mean_hrr</x:v>
+      </x:c>
+      <x:c r="C6" s="58" t="str">
+        <x:v>0.8546319656964558</x:v>
+      </x:c>
+      <x:c r="D6" s="58" t="str">
+        <x:v>0.7441318183951224</x:v>
+      </x:c>
+      <x:c r="E6" s="58" t="str">
+        <x:v>0.9277866378177638</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="20" t="str">
+        <x:v>within_participant_pearson</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>thrr_i</x:v>
+      </x:c>
+      <x:c r="C7" s="37" t="str">
+        <x:v>0.860885987121703</x:v>
+      </x:c>
+      <x:c r="D7" s="37" t="str">
+        <x:v>0.7655254396710821</x:v>
+      </x:c>
+      <x:c r="E7" s="37" t="str">
+        <x:v>0.9313685567073998</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="57" t="str">
+        <x:v>within_participant_pearson</x:v>
+      </x:c>
+      <x:c r="B8" s="57" t="str">
+        <x:v>delta_tilt</x:v>
+      </x:c>
+      <x:c r="C8" s="58" t="str">
+        <x:v>0.38663276778422656</x:v>
+      </x:c>
+      <x:c r="D8" s="58" t="str">
+        <x:v>0.20298892010398278</x:v>
+      </x:c>
+      <x:c r="E8" s="58" t="str">
+        <x:v>0.5808226895170263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="20" t="str">
+        <x:v>within_participant_pearson</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>thrr_i_minus_mean_hrr</x:v>
+      </x:c>
+      <x:c r="C9" s="37" t="str">
+        <x:v>0.006254021425247114</x:v>
+      </x:c>
+      <x:c r="D9" s="37" t="str">
+        <x:v>-0.007539442803931973</x:v>
+      </x:c>
+      <x:c r="E9" s="37" t="str">
+        <x:v>0.027030779411350403</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="57" t="str">
+        <x:v>between_participant_pearson</x:v>
+      </x:c>
+      <x:c r="B10" s="57" t="str">
+        <x:v>mean_hrr</x:v>
+      </x:c>
+      <x:c r="C10" s="58" t="str">
+        <x:v>0.6572996519113509</x:v>
+      </x:c>
+      <x:c r="D10" s="58" t="str">
+        <x:v>0.3713482444108191</x:v>
+      </x:c>
+      <x:c r="E10" s="58" t="str">
+        <x:v>0.8627671997757188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="20" t="str">
+        <x:v>between_participant_pearson</x:v>
+      </x:c>
+      <x:c r="B11" s="20" t="str">
+        <x:v>thrr_i</x:v>
+      </x:c>
+      <x:c r="C11" s="37" t="str">
+        <x:v>0.64270898131526</x:v>
+      </x:c>
+      <x:c r="D11" s="37" t="str">
+        <x:v>0.35681692026959305</x:v>
+      </x:c>
+      <x:c r="E11" s="37" t="str">
+        <x:v>0.8522905514640665</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="57" t="str">
+        <x:v>between_participant_pearson</x:v>
+      </x:c>
+      <x:c r="B12" s="57" t="str">
+        <x:v>delta_tilt</x:v>
+      </x:c>
+      <x:c r="C12" s="58" t="str">
+        <x:v>0.3098035237117446</x:v>
+      </x:c>
+      <x:c r="D12" s="58" t="str">
+        <x:v>-0.13798605947614453</x:v>
+      </x:c>
+      <x:c r="E12" s="58" t="str">
+        <x:v>0.6865774016938055</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="20" t="str">
+        <x:v>between_participant_pearson</x:v>
+      </x:c>
+      <x:c r="B13" s="20" t="str">
+        <x:v>thrr_i_minus_mean_hrr</x:v>
+      </x:c>
+      <x:c r="C13" s="37" t="str">
+        <x:v>-0.014590670596090871</x:v>
+      </x:c>
+      <x:c r="D13" s="37" t="str">
+        <x:v>-0.06680728664874591</x:v>
+      </x:c>
+      <x:c r="E13" s="37" t="str">
+        <x:v>0.03572629905841127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="57" t="str">
+        <x:v>participant_and_stage_residual_pearson</x:v>
+      </x:c>
+      <x:c r="B14" s="57" t="str">
+        <x:v>mean_hrr</x:v>
+      </x:c>
+      <x:c r="C14" s="58" t="str">
+        <x:v>0.3674099816895352</x:v>
+      </x:c>
+      <x:c r="D14" s="58" t="str">
+        <x:v>-0.02325058821849159</x:v>
+      </x:c>
+      <x:c r="E14" s="58" t="str">
+        <x:v>0.6778878694625549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="20" t="str">
+        <x:v>participant_and_stage_residual_pearson</x:v>
+      </x:c>
+      <x:c r="B15" s="20" t="str">
+        <x:v>thrr_i</x:v>
+      </x:c>
+      <x:c r="C15" s="37" t="str">
+        <x:v>0.3623037457003745</x:v>
+      </x:c>
+      <x:c r="D15" s="37" t="str">
+        <x:v>0.0018644647749262641</x:v>
+      </x:c>
+      <x:c r="E15" s="37" t="str">
+        <x:v>0.6621359382872389</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="57" t="str">
+        <x:v>participant_and_stage_residual_pearson</x:v>
+      </x:c>
+      <x:c r="B16" s="57" t="str">
+        <x:v>delta_tilt</x:v>
+      </x:c>
+      <x:c r="C16" s="58" t="str">
+        <x:v>0.060505058184702164</x:v>
+      </x:c>
+      <x:c r="D16" s="58" t="str">
+        <x:v>-0.10136199385679816</x:v>
+      </x:c>
+      <x:c r="E16" s="58" t="str">
+        <x:v>0.21825212028355184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="20" t="str">
+        <x:v>participant_and_stage_residual_pearson</x:v>
+      </x:c>
+      <x:c r="B17" s="20" t="str">
+        <x:v>thrr_i_minus_mean_hrr</x:v>
+      </x:c>
+      <x:c r="C17" s="37" t="str">
+        <x:v>-0.005106235989160712</x:v>
+      </x:c>
+      <x:c r="D17" s="37" t="str">
+        <x:v>-0.05149517046910237</x:v>
+      </x:c>
+      <x:c r="E17" s="37" t="str">
+        <x:v>0.04244356944209188</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="58" hidden="0" customHeight="1">
+      <x:c r="A1" s="54" t="str">
+        <x:v>device</x:v>
+      </x:c>
+      <x:c r="B1" s="55" t="str">
+        <x:v>score</x:v>
+      </x:c>
+      <x:c r="C1" s="55" t="str">
+        <x:v>participants</x:v>
+      </x:c>
+      <x:c r="D1" s="55" t="str">
+        <x:v>stages</x:v>
+      </x:c>
+      <x:c r="E1" s="55" t="str">
+        <x:v>bias</x:v>
+      </x:c>
+      <x:c r="F1" s="55" t="str">
+        <x:v>mae</x:v>
+      </x:c>
+      <x:c r="G1" s="55" t="str">
+        <x:v>rmse</x:v>
+      </x:c>
+      <x:c r="H1" s="55" t="str">
+        <x:v>icc_a1</x:v>
+      </x:c>
+      <x:c r="I1" s="55" t="str">
+        <x:v>loa_lower</x:v>
+      </x:c>
+      <x:c r="J1" s="56" t="str">
+        <x:v>loa_upper</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="57" t="str">
+        <x:v>apple_watch</x:v>
+      </x:c>
+      <x:c r="B2" s="57" t="str">
+        <x:v>mean_hrr</x:v>
+      </x:c>
+      <x:c r="C2" s="59" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="58" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E2" s="58" t="str">
+        <x:v>-0.42749684422358447</x:v>
+      </x:c>
+      <x:c r="F2" s="58" t="str">
+        <x:v>0.42749684422358447</x:v>
+      </x:c>
+      <x:c r="G2" s="58" t="str">
+        <x:v>0.43158110495191554</x:v>
+      </x:c>
+      <x:c r="H2" s="58" t="str"/>
+      <x:c r="I2" s="58" t="str">
+        <x:v>-0.5916858542457937</x:v>
+      </x:c>
+      <x:c r="J2" s="58" t="str">
+        <x:v>-0.2633078342013752</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="20" t="str">
+        <x:v>apple_watch</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>thrr_i</x:v>
+      </x:c>
+      <x:c r="C3" s="39" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3" s="37" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E3" s="37" t="str">
+        <x:v>-0.41203174767140543</x:v>
+      </x:c>
+      <x:c r="F3" s="37" t="str">
+        <x:v>0.41203174767140543</x:v>
+      </x:c>
+      <x:c r="G3" s="37" t="str">
+        <x:v>0.4176224207427514</x:v>
+      </x:c>
+      <x:c r="H3" s="37" t="str"/>
+      <x:c r="I3" s="37" t="str">
+        <x:v>-0.6008098722357699</x:v>
+      </x:c>
+      <x:c r="J3" s="37" t="str">
+        <x:v>-0.223253623107041</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="57" t="str">
+        <x:v>apple_watch</x:v>
+      </x:c>
+      <x:c r="B4" s="57" t="str">
+        <x:v>delta_tilt</x:v>
+      </x:c>
+      <x:c r="C4" s="59" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D4" s="58" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E4" s="58" t="str">
+        <x:v>0.015465096552179081</x:v>
+      </x:c>
+      <x:c r="F4" s="58" t="str">
+        <x:v>0.015465096552179081</x:v>
+      </x:c>
+      <x:c r="G4" s="58" t="str">
+        <x:v>0.017828728993214197</x:v>
+      </x:c>
+      <x:c r="H4" s="58" t="str"/>
+      <x:c r="I4" s="58" t="str">
+        <x:v>-0.009124017989976044</x:v>
+      </x:c>
+      <x:c r="J4" s="58" t="str">
+        <x:v>0.040054211094334206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="20" t="str">
+        <x:v>e4</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>mean_hrr</x:v>
+      </x:c>
+      <x:c r="C5" s="39" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D5" s="37" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E5" s="37" t="str">
+        <x:v>0.011972552195592248</x:v>
+      </x:c>
+      <x:c r="F5" s="37" t="str">
+        <x:v>0.20297385118945713</x:v>
+      </x:c>
+      <x:c r="G5" s="37" t="str">
+        <x:v>0.21483103551726757</x:v>
+      </x:c>
+      <x:c r="H5" s="37" t="str">
+        <x:v>-0.41826481507905383</x:v>
+      </x:c>
+      <x:c r="I5" s="37" t="str">
+        <x:v>-0.4734802215072408</x:v>
+      </x:c>
+      <x:c r="J5" s="37" t="str">
+        <x:v>0.49742532589842525</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="57" t="str">
+        <x:v>e4</x:v>
+      </x:c>
+      <x:c r="B6" s="57" t="str">
+        <x:v>thrr_i</x:v>
+      </x:c>
+      <x:c r="C6" s="59" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="58" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E6" s="58" t="str">
+        <x:v>0.2975935262406313</x:v>
+      </x:c>
+      <x:c r="F6" s="58" t="str">
+        <x:v>0.3951927525415927</x:v>
+      </x:c>
+      <x:c r="G6" s="58" t="str">
+        <x:v>0.49906660508374034</x:v>
+      </x:c>
+      <x:c r="H6" s="58" t="str">
+        <x:v>-0.6948036667708133</x:v>
+      </x:c>
+      <x:c r="I6" s="58" t="str">
+        <x:v>-0.6091208320127346</x:v>
+      </x:c>
+      <x:c r="J6" s="58" t="str">
+        <x:v>1.2043078844939972</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="20" t="str">
+        <x:v>e4</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>delta_tilt</x:v>
+      </x:c>
+      <x:c r="C7" s="39" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="37" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="37" t="str">
+        <x:v>0.2856209740450391</x:v>
+      </x:c>
+      <x:c r="F7" s="37" t="str">
+        <x:v>0.2856209740450391</x:v>
+      </x:c>
+      <x:c r="G7" s="37" t="str">
+        <x:v>0.3431084881097535</x:v>
+      </x:c>
+      <x:c r="H7" s="37" t="str">
+        <x:v>0.03165385730904518</x:v>
+      </x:c>
+      <x:c r="I7" s="37" t="str">
+        <x:v>-0.14465204120056752</x:v>
+      </x:c>
+      <x:c r="J7" s="37" t="str">
+        <x:v>0.7158939892906457</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="B8" s="57" t="str">
+        <x:v>mean_hrr</x:v>
+      </x:c>
+      <x:c r="C8" s="59" t="str">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" s="58" t="str">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E8" s="58" t="str">
+        <x:v>-0.0261244166569313</x:v>
+      </x:c>
+      <x:c r="F8" s="58" t="str">
+        <x:v>0.045083191358778245</x:v>
+      </x:c>
+      <x:c r="G8" s="58" t="str">
+        <x:v>0.08061847104747495</x:v>
+      </x:c>
+      <x:c r="H8" s="58" t="str">
+        <x:v>0.9195611447558282</x:v>
+      </x:c>
+      <x:c r="I8" s="58" t="str">
+        <x:v>-0.17659051928210334</x:v>
+      </x:c>
+      <x:c r="J8" s="58" t="str">
+        <x:v>0.12434168596824074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>thrr_i</x:v>
+      </x:c>
+      <x:c r="C9" s="39" t="str">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D9" s="37" t="str">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E9" s="37" t="str">
+        <x:v>-0.025876729060699183</x:v>
+      </x:c>
+      <x:c r="F9" s="37" t="str">
+        <x:v>0.06342023085181096</x:v>
+      </x:c>
+      <x:c r="G9" s="37" t="str">
+        <x:v>0.11982451816305033</x:v>
+      </x:c>
+      <x:c r="H9" s="37" t="str">
+        <x:v>0.8537184867022254</x:v>
+      </x:c>
+      <x:c r="I9" s="37" t="str">
+        <x:v>-0.2566946658077425</x:v>
+      </x:c>
+      <x:c r="J9" s="37" t="str">
+        <x:v>0.2049412076863441</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="B10" s="57" t="str">
+        <x:v>delta_tilt</x:v>
+      </x:c>
+      <x:c r="C10" s="59" t="str">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D10" s="58" t="str">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E10" s="58" t="str">
+        <x:v>0.0002476875962321063</x:v>
+      </x:c>
+      <x:c r="F10" s="58" t="str">
+        <x:v>0.0297030632801438</x:v>
+      </x:c>
+      <x:c r="G10" s="58" t="str">
+        <x:v>0.05722892097705491</x:v>
+      </x:c>
+      <x:c r="H10" s="58" t="str">
+        <x:v>0.17890807341540707</x:v>
+      </x:c>
+      <x:c r="I10" s="58" t="str">
+        <x:v>-0.11265548031186201</x:v>
+      </x:c>
+      <x:c r="J10" s="58" t="str">
+        <x:v>0.11315085550432621</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="58" hidden="0" customHeight="1">
+      <x:c r="A1" s="54" t="str">
+        <x:v>device</x:v>
+      </x:c>
+      <x:c r="B1" s="55" t="str">
+        <x:v>score</x:v>
+      </x:c>
+      <x:c r="C1" s="55" t="str">
+        <x:v>bias_ci_low</x:v>
+      </x:c>
+      <x:c r="D1" s="55" t="str">
+        <x:v>bias_ci_high</x:v>
+      </x:c>
+      <x:c r="E1" s="55" t="str">
+        <x:v>mae_ci_low</x:v>
+      </x:c>
+      <x:c r="F1" s="55" t="str">
+        <x:v>mae_ci_high</x:v>
+      </x:c>
+      <x:c r="G1" s="55" t="str">
+        <x:v>icc_a1_ci_low</x:v>
+      </x:c>
+      <x:c r="H1" s="55" t="str">
+        <x:v>icc_a1_ci_high</x:v>
+      </x:c>
+      <x:c r="I1" s="55" t="str">
+        <x:v>loa_lower_ci_low</x:v>
+      </x:c>
+      <x:c r="J1" s="55" t="str">
+        <x:v>loa_lower_ci_high</x:v>
+      </x:c>
+      <x:c r="K1" s="55" t="str">
+        <x:v>loa_upper_ci_low</x:v>
+      </x:c>
+      <x:c r="L1" s="56" t="str">
+        <x:v>loa_upper_ci_high</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="57" t="str">
+        <x:v>apple_watch</x:v>
+      </x:c>
+      <x:c r="B2" s="57" t="str">
+        <x:v>mean_hrr</x:v>
+      </x:c>
+      <x:c r="C2" s="58" t="str">
+        <x:v>-0.42749684422358447</x:v>
+      </x:c>
+      <x:c r="D2" s="58" t="str">
+        <x:v>-0.42749684422358447</x:v>
+      </x:c>
+      <x:c r="E2" s="58" t="str">
+        <x:v>0.42749684422358447</x:v>
+      </x:c>
+      <x:c r="F2" s="58" t="str">
+        <x:v>0.42749684422358447</x:v>
+      </x:c>
+      <x:c r="G2" s="58" t="str"/>
+      <x:c r="H2" s="58" t="str"/>
+      <x:c r="I2" s="58" t="str">
+        <x:v>-0.5916858542457937</x:v>
+      </x:c>
+      <x:c r="J2" s="58" t="str">
+        <x:v>-0.5916858542457937</x:v>
+      </x:c>
+      <x:c r="K2" s="58" t="str">
+        <x:v>-0.2633078342013752</x:v>
+      </x:c>
+      <x:c r="L2" s="58" t="str">
+        <x:v>-0.2633078342013752</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="20" t="str">
+        <x:v>apple_watch</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>thrr_i</x:v>
+      </x:c>
+      <x:c r="C3" s="37" t="str">
+        <x:v>-0.41203174767140543</x:v>
+      </x:c>
+      <x:c r="D3" s="37" t="str">
+        <x:v>-0.41203174767140543</x:v>
+      </x:c>
+      <x:c r="E3" s="37" t="str">
+        <x:v>0.41203174767140543</x:v>
+      </x:c>
+      <x:c r="F3" s="37" t="str">
+        <x:v>0.41203174767140543</x:v>
+      </x:c>
+      <x:c r="G3" s="37" t="str"/>
+      <x:c r="H3" s="37" t="str"/>
+      <x:c r="I3" s="37" t="str">
+        <x:v>-0.6008098722357699</x:v>
+      </x:c>
+      <x:c r="J3" s="37" t="str">
+        <x:v>-0.6008098722357699</x:v>
+      </x:c>
+      <x:c r="K3" s="37" t="str">
+        <x:v>-0.223253623107041</x:v>
+      </x:c>
+      <x:c r="L3" s="37" t="str">
+        <x:v>-0.223253623107041</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="57" t="str">
+        <x:v>apple_watch</x:v>
+      </x:c>
+      <x:c r="B4" s="57" t="str">
+        <x:v>delta_tilt</x:v>
+      </x:c>
+      <x:c r="C4" s="58" t="str">
+        <x:v>0.015465096552179081</x:v>
+      </x:c>
+      <x:c r="D4" s="58" t="str">
+        <x:v>0.015465096552179081</x:v>
+      </x:c>
+      <x:c r="E4" s="58" t="str">
+        <x:v>0.015465096552179081</x:v>
+      </x:c>
+      <x:c r="F4" s="58" t="str">
+        <x:v>0.015465096552179081</x:v>
+      </x:c>
+      <x:c r="G4" s="58" t="str"/>
+      <x:c r="H4" s="58" t="str"/>
+      <x:c r="I4" s="58" t="str">
+        <x:v>-0.009124017989976044</x:v>
+      </x:c>
+      <x:c r="J4" s="58" t="str">
+        <x:v>-0.009124017989976044</x:v>
+      </x:c>
+      <x:c r="K4" s="58" t="str">
+        <x:v>0.040054211094334206</x:v>
+      </x:c>
+      <x:c r="L4" s="58" t="str">
+        <x:v>0.040054211094334206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="20" t="str">
+        <x:v>e4</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>mean_hrr</x:v>
+      </x:c>
+      <x:c r="C5" s="37" t="str">
+        <x:v>-0.1910012989938649</x:v>
+      </x:c>
+      <x:c r="D5" s="37" t="str">
+        <x:v>0.2149464033850494</x:v>
+      </x:c>
+      <x:c r="E5" s="37" t="str">
+        <x:v>0.1910012989938649</x:v>
+      </x:c>
+      <x:c r="F5" s="37" t="str">
+        <x:v>0.2149464033850494</x:v>
+      </x:c>
+      <x:c r="G5" s="37" t="str">
+        <x:v>-0.41826481507905383</x:v>
+      </x:c>
+      <x:c r="H5" s="37" t="str">
+        <x:v>0.03552200670555849</x:v>
+      </x:c>
+      <x:c r="I5" s="37" t="str">
+        <x:v>-0.4734802215072408</x:v>
+      </x:c>
+      <x:c r="J5" s="37" t="str">
+        <x:v>0.0344926696405779</x:v>
+      </x:c>
+      <x:c r="K5" s="37" t="str">
+        <x:v>-0.061703169442219236</x:v>
+      </x:c>
+      <x:c r="L5" s="37" t="str">
+        <x:v>0.49742532589842525</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="57" t="str">
+        <x:v>e4</x:v>
+      </x:c>
+      <x:c r="B6" s="57" t="str">
+        <x:v>thrr_i</x:v>
+      </x:c>
+      <x:c r="C6" s="58" t="str">
+        <x:v>-0.0927581153138006</x:v>
+      </x:c>
+      <x:c r="D6" s="58" t="str">
+        <x:v>0.6879451677950632</x:v>
+      </x:c>
+      <x:c r="E6" s="58" t="str">
+        <x:v>0.10244033728812216</x:v>
+      </x:c>
+      <x:c r="F6" s="58" t="str">
+        <x:v>0.6879451677950632</x:v>
+      </x:c>
+      <x:c r="G6" s="58" t="str">
+        <x:v>-0.6948036667708133</x:v>
+      </x:c>
+      <x:c r="H6" s="58" t="str">
+        <x:v>-0.0022184339220257484</x:v>
+      </x:c>
+      <x:c r="I6" s="58" t="str">
+        <x:v>-0.6091208320127346</x:v>
+      </x:c>
+      <x:c r="J6" s="58" t="str">
+        <x:v>0.5160555432514714</x:v>
+      </x:c>
+      <x:c r="K6" s="58" t="str">
+        <x:v>0.13908619341815906</x:v>
+      </x:c>
+      <x:c r="L6" s="58" t="str">
+        <x:v>1.2043078844939972</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="20" t="str">
+        <x:v>e4</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>delta_tilt</x:v>
+      </x:c>
+      <x:c r="C7" s="37" t="str">
+        <x:v>0.0982431836800643</x:v>
+      </x:c>
+      <x:c r="D7" s="37" t="str">
+        <x:v>0.47299876441001387</x:v>
+      </x:c>
+      <x:c r="E7" s="37" t="str">
+        <x:v>0.0982431836800643</x:v>
+      </x:c>
+      <x:c r="F7" s="37" t="str">
+        <x:v>0.47299876441001387</x:v>
+      </x:c>
+      <x:c r="G7" s="37" t="str">
+        <x:v>-0.0868803747587226</x:v>
+      </x:c>
+      <x:c r="H7" s="37" t="str">
+        <x:v>0.0316538573090452</x:v>
+      </x:c>
+      <x:c r="I7" s="37" t="str">
+        <x:v>-0.14465204120056752</x:v>
+      </x:c>
+      <x:c r="J7" s="37" t="str">
+        <x:v>0.4644346552091342</x:v>
+      </x:c>
+      <x:c r="K7" s="37" t="str">
+        <x:v>0.2007893628603783</x:v>
+      </x:c>
+      <x:c r="L7" s="37" t="str">
+        <x:v>0.7158939892906457</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="B8" s="57" t="str">
+        <x:v>mean_hrr</x:v>
+      </x:c>
+      <x:c r="C8" s="58" t="str">
+        <x:v>-0.03783940290490184</x:v>
+      </x:c>
+      <x:c r="D8" s="58" t="str">
+        <x:v>-0.010666668910327672</x:v>
+      </x:c>
+      <x:c r="E8" s="58" t="str">
+        <x:v>0.030891574141106375</x:v>
+      </x:c>
+      <x:c r="F8" s="58" t="str">
+        <x:v>0.06264431187002908</x:v>
+      </x:c>
+      <x:c r="G8" s="58" t="str">
+        <x:v>0.7910909611743817</x:v>
+      </x:c>
+      <x:c r="H8" s="58" t="str">
+        <x:v>0.9744889337232496</x:v>
+      </x:c>
+      <x:c r="I8" s="58" t="str">
+        <x:v>-0.23436323864562403</x:v>
+      </x:c>
+      <x:c r="J8" s="58" t="str">
+        <x:v>-0.10363618860690428</x:v>
+      </x:c>
+      <x:c r="K8" s="58" t="str">
+        <x:v>0.04336376577297059</x:v>
+      </x:c>
+      <x:c r="L8" s="58" t="str">
+        <x:v>0.20742473141765982</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>thrr_i</x:v>
+      </x:c>
+      <x:c r="C9" s="37" t="str">
+        <x:v>-0.04641816007457109</x:v>
+      </x:c>
+      <x:c r="D9" s="37" t="str">
+        <x:v>-0.0011997786021330538</x:v>
+      </x:c>
+      <x:c r="E9" s="37" t="str">
+        <x:v>0.043384270050672864</x:v>
+      </x:c>
+      <x:c r="F9" s="37" t="str">
+        <x:v>0.08594269661364508</x:v>
+      </x:c>
+      <x:c r="G9" s="37" t="str">
+        <x:v>0.6666555346750416</x:v>
+      </x:c>
+      <x:c r="H9" s="37" t="str">
+        <x:v>0.9520559069099573</x:v>
+      </x:c>
+      <x:c r="I9" s="37" t="str">
+        <x:v>-0.32647245245331263</x:v>
+      </x:c>
+      <x:c r="J9" s="37" t="str">
+        <x:v>-0.15786516919619922</x:v>
+      </x:c>
+      <x:c r="K9" s="37" t="str">
+        <x:v>0.07325146812647847</x:v>
+      </x:c>
+      <x:c r="L9" s="37" t="str">
+        <x:v>0.3176989056207694</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="B10" s="57" t="str">
+        <x:v>delta_tilt</x:v>
+      </x:c>
+      <x:c r="C10" s="58" t="str">
+        <x:v>-0.01227727728800503</x:v>
+      </x:c>
+      <x:c r="D10" s="58" t="str">
+        <x:v>0.01521011792117622</x:v>
+      </x:c>
+      <x:c r="E10" s="58" t="str">
+        <x:v>0.019939669949900596</x:v>
+      </x:c>
+      <x:c r="F10" s="58" t="str">
+        <x:v>0.042173823916910456</x:v>
+      </x:c>
+      <x:c r="G10" s="58" t="str">
+        <x:v>-0.013310921853150307</x:v>
+      </x:c>
+      <x:c r="H10" s="58" t="str">
+        <x:v>0.4934934252423442</x:v>
+      </x:c>
+      <x:c r="I10" s="58" t="str">
+        <x:v>-0.14620890934748376</x:v>
+      </x:c>
+      <x:c r="J10" s="58" t="str">
+        <x:v>-0.07304263056600116</x:v>
+      </x:c>
+      <x:c r="K10" s="58" t="str">
+        <x:v>0.05435635607952811</x:v>
+      </x:c>
+      <x:c r="L10" s="58" t="str">
+        <x:v>0.1618964125941942</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="58" hidden="0" customHeight="1">
+      <x:c r="A1" s="54" t="str">
+        <x:v>participant</x:v>
+      </x:c>
+      <x:c r="B1" s="55" t="str">
+        <x:v>stage</x:v>
+      </x:c>
+      <x:c r="C1" s="55" t="str">
+        <x:v>device</x:v>
+      </x:c>
+      <x:c r="D1" s="55" t="str">
+        <x:v>device_samples</x:v>
+      </x:c>
+      <x:c r="E1" s="55" t="str">
+        <x:v>timestamp_samples_matched_within_2s_percent</x:v>
+      </x:c>
+      <x:c r="F1" s="55" t="str">
+        <x:v>median_signed_nearest_timestamp_offset_s</x:v>
+      </x:c>
+      <x:c r="G1" s="55" t="str">
+        <x:v>median_absolute_nearest_timestamp_offset_s</x:v>
+      </x:c>
+      <x:c r="H1" s="55" t="str">
+        <x:v>p95_absolute_nearest_timestamp_offset_s</x:v>
+      </x:c>
+      <x:c r="I1" s="56" t="str">
+        <x:v>optimal_hr_cross_correlation_lag_s</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="57" t="str">
+        <x:v>P01</x:v>
+      </x:c>
+      <x:c r="B2" s="57" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C2" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D2" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E2" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F2" s="58" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="G2" s="58" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="H2" s="58" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="I2" s="58" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="20" t="str">
+        <x:v>P01</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C3" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D3" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E3" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F3" s="37" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="G3" s="37" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="H3" s="37" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="I3" s="37" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="57" t="str">
+        <x:v>P01</x:v>
+      </x:c>
+      <x:c r="B4" s="57" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C4" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D4" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E4" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F4" s="58" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="G4" s="58" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="H4" s="58" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="I4" s="58" t="str">
+        <x:v>3.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="20" t="str">
+        <x:v>P01</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D5" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E5" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F5" s="37" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="G5" s="37" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="H5" s="37" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="I5" s="37" t="str">
+        <x:v>-1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="57" t="str">
+        <x:v>P01</x:v>
+      </x:c>
+      <x:c r="B6" s="57" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C6" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D6" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E6" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F6" s="58" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="G6" s="58" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="H6" s="58" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="I6" s="58" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="20" t="str">
+        <x:v>P01</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>run_high</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D7" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E7" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F7" s="37" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="G7" s="37" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="H7" s="37" t="str">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="I7" s="37" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="57" t="str">
+        <x:v>P02</x:v>
+      </x:c>
+      <x:c r="B8" s="57" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C8" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D8" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E8" s="59" t="str">
+        <x:v>86.33333333333333</x:v>
+      </x:c>
+      <x:c r="F8" s="58" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="G8" s="58" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="H8" s="58" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="I8" s="58" t="str">
+        <x:v>13.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="20" t="str">
+        <x:v>P02</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D9" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E9" s="39" t="str">
+        <x:v>96.0</x:v>
+      </x:c>
+      <x:c r="F9" s="37" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="G9" s="37" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="H9" s="37" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="I9" s="37" t="str">
+        <x:v>5.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="57" t="str">
+        <x:v>P02</x:v>
+      </x:c>
+      <x:c r="B10" s="57" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C10" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D10" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E10" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F10" s="58" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="G10" s="58" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="H10" s="58" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="I10" s="58" t="str">
+        <x:v>-11.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="20" t="str">
+        <x:v>P02</x:v>
+      </x:c>
+      <x:c r="B11" s="20" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C11" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D11" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E11" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F11" s="37" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="G11" s="37" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="H11" s="37" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="I11" s="37" t="str">
+        <x:v>7.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="57" t="str">
+        <x:v>P02</x:v>
+      </x:c>
+      <x:c r="B12" s="57" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C12" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D12" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E12" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F12" s="58" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="G12" s="58" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="H12" s="58" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="I12" s="58" t="str">
+        <x:v>-9.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="20" t="str">
+        <x:v>P02</x:v>
+      </x:c>
+      <x:c r="B13" s="20" t="str">
+        <x:v>run_high</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D13" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E13" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F13" s="37" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="G13" s="37" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="H13" s="37" t="str">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="I13" s="37" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="57" t="str">
+        <x:v>P03</x:v>
+      </x:c>
+      <x:c r="B14" s="57" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C14" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D14" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E14" s="59" t="str">
+        <x:v>98.33333333333333</x:v>
+      </x:c>
+      <x:c r="F14" s="58" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="G14" s="58" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="H14" s="58" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="I14" s="58" t="str">
+        <x:v>11.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="20" t="str">
+        <x:v>P03</x:v>
+      </x:c>
+      <x:c r="B15" s="20" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D15" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E15" s="39" t="str">
+        <x:v>91.33333333333333</x:v>
+      </x:c>
+      <x:c r="F15" s="37" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="G15" s="37" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="H15" s="37" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="I15" s="37" t="str">
+        <x:v>8.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="57" t="str">
+        <x:v>P03</x:v>
+      </x:c>
+      <x:c r="B16" s="57" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C16" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D16" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E16" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F16" s="58" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="G16" s="58" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="H16" s="58" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="I16" s="58" t="str">
+        <x:v>-4.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="20" t="str">
+        <x:v>P03</x:v>
+      </x:c>
+      <x:c r="B17" s="20" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C17" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D17" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E17" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F17" s="37" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="G17" s="37" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="H17" s="37" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="I17" s="37" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="57" t="str">
+        <x:v>P03</x:v>
+      </x:c>
+      <x:c r="B18" s="57" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C18" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D18" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E18" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F18" s="58" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="G18" s="58" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="H18" s="58" t="str">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="I18" s="58" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="20" t="str">
+        <x:v>P04</x:v>
+      </x:c>
+      <x:c r="B19" s="20" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C19" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D19" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E19" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F19" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="G19" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="H19" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="I19" s="37" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="57" t="str">
+        <x:v>P04</x:v>
+      </x:c>
+      <x:c r="B20" s="57" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C20" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D20" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E20" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F20" s="58" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="G20" s="58" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="H20" s="58" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="I20" s="58" t="str">
+        <x:v>9.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="20" t="str">
+        <x:v>P04</x:v>
+      </x:c>
+      <x:c r="B21" s="20" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C21" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D21" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E21" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F21" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="G21" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="H21" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="I21" s="37" t="str">
+        <x:v>-1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="57" t="str">
+        <x:v>P04</x:v>
+      </x:c>
+      <x:c r="B22" s="57" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C22" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D22" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E22" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F22" s="58" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="G22" s="58" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="H22" s="58" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="I22" s="58" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" s="20" t="str">
+        <x:v>P04</x:v>
+      </x:c>
+      <x:c r="B23" s="20" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C23" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D23" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E23" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F23" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="G23" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="H23" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="I23" s="37" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="57" t="str">
+        <x:v>P05</x:v>
+      </x:c>
+      <x:c r="B24" s="57" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C24" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D24" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E24" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F24" s="58" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="G24" s="58" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="H24" s="58" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="I24" s="58" t="str">
+        <x:v>7.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="20" t="str">
+        <x:v>P05</x:v>
+      </x:c>
+      <x:c r="B25" s="20" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C25" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D25" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E25" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F25" s="37" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="G25" s="37" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="H25" s="37" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="I25" s="37" t="str">
+        <x:v>4.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="57" t="str">
+        <x:v>P05</x:v>
+      </x:c>
+      <x:c r="B26" s="57" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C26" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D26" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E26" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F26" s="58" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="G26" s="58" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="H26" s="58" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="I26" s="58" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="20" t="str">
+        <x:v>P05</x:v>
+      </x:c>
+      <x:c r="B27" s="20" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C27" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D27" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E27" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F27" s="37" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="G27" s="37" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="H27" s="37" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="I27" s="37" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="57" t="str">
+        <x:v>P05</x:v>
+      </x:c>
+      <x:c r="B28" s="57" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C28" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D28" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E28" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F28" s="58" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="G28" s="58" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="H28" s="58" t="str">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="I28" s="58" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="20" t="str">
+        <x:v>P06</x:v>
+      </x:c>
+      <x:c r="B29" s="20" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C29" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D29" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E29" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F29" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="G29" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="H29" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="I29" s="37" t="str">
+        <x:v>14.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="57" t="str">
+        <x:v>P06</x:v>
+      </x:c>
+      <x:c r="B30" s="57" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C30" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D30" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E30" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F30" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="G30" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="H30" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="I30" s="58" t="str">
+        <x:v>13.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="20" t="str">
+        <x:v>P06</x:v>
+      </x:c>
+      <x:c r="B31" s="20" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C31" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D31" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E31" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F31" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="G31" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="H31" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="I31" s="37" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="57" t="str">
+        <x:v>P06</x:v>
+      </x:c>
+      <x:c r="B32" s="57" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C32" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D32" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E32" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F32" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="G32" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="H32" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="I32" s="58" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" s="20" t="str">
+        <x:v>P06</x:v>
+      </x:c>
+      <x:c r="B33" s="20" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C33" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D33" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E33" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F33" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="G33" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="H33" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="I33" s="37" t="str">
+        <x:v>9.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" s="57" t="str">
+        <x:v>P07</x:v>
+      </x:c>
+      <x:c r="B34" s="57" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C34" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D34" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E34" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F34" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="G34" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="H34" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="I34" s="58" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
+      <x:c r="A35" s="20" t="str">
+        <x:v>P07</x:v>
+      </x:c>
+      <x:c r="B35" s="20" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C35" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D35" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E35" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F35" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="G35" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="H35" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="I35" s="37" t="str">
+        <x:v>13.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
+      <x:c r="A36" s="57" t="str">
+        <x:v>P07</x:v>
+      </x:c>
+      <x:c r="B36" s="57" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C36" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D36" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E36" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F36" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="G36" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="H36" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="I36" s="58" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
+      <x:c r="A37" s="20" t="str">
+        <x:v>P07</x:v>
+      </x:c>
+      <x:c r="B37" s="20" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C37" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F37" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="G37" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="H37" s="37" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="I37" s="37" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
+      <x:c r="A38" s="57" t="str">
+        <x:v>P07</x:v>
+      </x:c>
+      <x:c r="B38" s="57" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C38" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D38" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E38" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F38" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="G38" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="H38" s="58" t="str">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="I38" s="58" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
+      <x:c r="A39" s="20" t="str">
+        <x:v>P08</x:v>
+      </x:c>
+      <x:c r="B39" s="20" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C39" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D39" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E39" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F39" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="G39" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="H39" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="I39" s="37" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="15" hidden="0" customHeight="1">
+      <x:c r="A40" s="57" t="str">
+        <x:v>P08</x:v>
+      </x:c>
+      <x:c r="B40" s="57" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C40" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D40" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E40" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F40" s="58" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="G40" s="58" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="H40" s="58" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="I40" s="58" t="str">
+        <x:v>14.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
+      <x:c r="A41" s="20" t="str">
+        <x:v>P08</x:v>
+      </x:c>
+      <x:c r="B41" s="20" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C41" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D41" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E41" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F41" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="G41" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="H41" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="I41" s="37" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="15" hidden="0" customHeight="1">
+      <x:c r="A42" s="57" t="str">
+        <x:v>P08</x:v>
+      </x:c>
+      <x:c r="B42" s="57" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C42" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D42" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E42" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F42" s="58" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="G42" s="58" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="H42" s="58" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="I42" s="58" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="15" hidden="0" customHeight="1">
+      <x:c r="A43" s="20" t="str">
+        <x:v>P08</x:v>
+      </x:c>
+      <x:c r="B43" s="20" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C43" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D43" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E43" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F43" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="G43" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="H43" s="37" t="str">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="I43" s="37" t="str">
+        <x:v>-4.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="15" hidden="0" customHeight="1">
+      <x:c r="A44" s="57" t="str">
+        <x:v>P09</x:v>
+      </x:c>
+      <x:c r="B44" s="57" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C44" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D44" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E44" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F44" s="58" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="G44" s="58" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="H44" s="58" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="I44" s="58" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="15" hidden="0" customHeight="1">
+      <x:c r="A45" s="20" t="str">
+        <x:v>P09</x:v>
+      </x:c>
+      <x:c r="B45" s="20" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C45" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D45" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E45" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F45" s="37" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="G45" s="37" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="H45" s="37" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="I45" s="37" t="str">
+        <x:v>10.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="15" hidden="0" customHeight="1">
+      <x:c r="A46" s="57" t="str">
+        <x:v>P09</x:v>
+      </x:c>
+      <x:c r="B46" s="57" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C46" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D46" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E46" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F46" s="58" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="G46" s="58" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="H46" s="58" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="I46" s="58" t="str">
+        <x:v>9.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="15" hidden="0" customHeight="1">
+      <x:c r="A47" s="20" t="str">
+        <x:v>P09</x:v>
+      </x:c>
+      <x:c r="B47" s="20" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C47" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D47" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E47" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F47" s="37" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="G47" s="37" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="H47" s="37" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="I47" s="37" t="str">
+        <x:v>4.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="15" hidden="0" customHeight="1">
+      <x:c r="A48" s="57" t="str">
+        <x:v>P09</x:v>
+      </x:c>
+      <x:c r="B48" s="57" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C48" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D48" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E48" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F48" s="58" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="G48" s="58" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="H48" s="58" t="str">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="I48" s="58" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="15" hidden="0" customHeight="1">
+      <x:c r="A49" s="20" t="str">
+        <x:v>P11</x:v>
+      </x:c>
+      <x:c r="B49" s="20" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C49" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D49" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E49" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F49" s="37" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="G49" s="37" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="H49" s="37" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="I49" s="37" t="str">
+        <x:v>5.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="15" hidden="0" customHeight="1">
+      <x:c r="A50" s="57" t="str">
+        <x:v>P11</x:v>
+      </x:c>
+      <x:c r="B50" s="57" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C50" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D50" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E50" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F50" s="58" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="G50" s="58" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="H50" s="58" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="I50" s="58" t="str">
+        <x:v>-7.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="15" hidden="0" customHeight="1">
+      <x:c r="A51" s="20" t="str">
+        <x:v>P11</x:v>
+      </x:c>
+      <x:c r="B51" s="20" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C51" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D51" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E51" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F51" s="37" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="G51" s="37" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="H51" s="37" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="I51" s="37" t="str">
+        <x:v>-10.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="15" hidden="0" customHeight="1">
+      <x:c r="A52" s="57" t="str">
+        <x:v>P11</x:v>
+      </x:c>
+      <x:c r="B52" s="57" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C52" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D52" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E52" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F52" s="58" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="G52" s="58" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="H52" s="58" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="I52" s="58" t="str">
+        <x:v>12.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="15" hidden="0" customHeight="1">
+      <x:c r="A53" s="20" t="str">
+        <x:v>P11</x:v>
+      </x:c>
+      <x:c r="B53" s="20" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C53" s="20" t="str">
+        <x:v>e4</x:v>
+      </x:c>
+      <x:c r="D53" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E53" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F53" s="37" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="G53" s="37" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="H53" s="37" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="I53" s="37" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="15" hidden="0" customHeight="1">
+      <x:c r="A54" s="57" t="str">
+        <x:v>P11</x:v>
+      </x:c>
+      <x:c r="B54" s="57" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C54" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D54" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E54" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F54" s="58" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="G54" s="58" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="H54" s="58" t="str">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="I54" s="58" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="15" hidden="0" customHeight="1">
+      <x:c r="A55" s="20" t="str">
+        <x:v>P11</x:v>
+      </x:c>
+      <x:c r="B55" s="20" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C55" s="20" t="str">
+        <x:v>e4</x:v>
+      </x:c>
+      <x:c r="D55" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E55" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F55" s="37" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="G55" s="37" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="H55" s="37" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="I55" s="37" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="15" hidden="0" customHeight="1">
+      <x:c r="A56" s="57" t="str">
+        <x:v>P12</x:v>
+      </x:c>
+      <x:c r="B56" s="57" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C56" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D56" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E56" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F56" s="58" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="G56" s="58" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="H56" s="58" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="I56" s="58" t="str">
+        <x:v>11.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="15" hidden="0" customHeight="1">
+      <x:c r="A57" s="20" t="str">
+        <x:v>P12</x:v>
+      </x:c>
+      <x:c r="B57" s="20" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C57" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D57" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E57" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F57" s="37" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="G57" s="37" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="H57" s="37" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="I57" s="37" t="str">
+        <x:v>3.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="15" hidden="0" customHeight="1">
+      <x:c r="A58" s="57" t="str">
+        <x:v>P12</x:v>
+      </x:c>
+      <x:c r="B58" s="57" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C58" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D58" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E58" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F58" s="58" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="G58" s="58" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="H58" s="58" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="I58" s="58" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="15" hidden="0" customHeight="1">
+      <x:c r="A59" s="20" t="str">
+        <x:v>P12</x:v>
+      </x:c>
+      <x:c r="B59" s="20" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C59" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D59" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E59" s="39" t="str">
+        <x:v>91.33333333333333</x:v>
+      </x:c>
+      <x:c r="F59" s="37" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="G59" s="37" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="H59" s="37" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="I59" s="37" t="str">
+        <x:v>8.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="15" hidden="0" customHeight="1">
+      <x:c r="A60" s="57" t="str">
+        <x:v>P12</x:v>
+      </x:c>
+      <x:c r="B60" s="57" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C60" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D60" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E60" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F60" s="58" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="G60" s="58" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="H60" s="58" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="I60" s="58" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="15" hidden="0" customHeight="1">
+      <x:c r="A61" s="20" t="str">
+        <x:v>P12</x:v>
+      </x:c>
+      <x:c r="B61" s="20" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C61" s="20" t="str">
+        <x:v>e4</x:v>
+      </x:c>
+      <x:c r="D61" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E61" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F61" s="37" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="G61" s="37" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="H61" s="37" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="I61" s="37" t="str">
+        <x:v>8.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="15" hidden="0" customHeight="1">
+      <x:c r="A62" s="57" t="str">
+        <x:v>P12</x:v>
+      </x:c>
+      <x:c r="B62" s="57" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C62" s="57" t="str">
+        <x:v>apple_watch</x:v>
+      </x:c>
+      <x:c r="D62" s="59" t="str">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E62" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F62" s="58" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="G62" s="58" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="H62" s="58" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="I62" s="58" t="str"/>
+    </x:row>
+    <x:row r="63" ht="15" hidden="0" customHeight="1">
+      <x:c r="A63" s="20" t="str">
+        <x:v>P12</x:v>
+      </x:c>
+      <x:c r="B63" s="20" t="str">
+        <x:v>run_high</x:v>
+      </x:c>
+      <x:c r="C63" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D63" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E63" s="39" t="str">
+        <x:v>85.0</x:v>
+      </x:c>
+      <x:c r="F63" s="37" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="G63" s="37" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="H63" s="37" t="str">
+        <x:v>0.444</x:v>
+      </x:c>
+      <x:c r="I63" s="37" t="str">
+        <x:v>-1.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="15" hidden="0" customHeight="1">
+      <x:c r="A64" s="57" t="str">
+        <x:v>P12</x:v>
+      </x:c>
+      <x:c r="B64" s="57" t="str">
+        <x:v>run_high</x:v>
+      </x:c>
+      <x:c r="C64" s="57" t="str">
+        <x:v>e4</x:v>
+      </x:c>
+      <x:c r="D64" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E64" s="59" t="str">
+        <x:v>85.33333333333334</x:v>
+      </x:c>
+      <x:c r="F64" s="58" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="G64" s="58" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="H64" s="58" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="I64" s="58" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="15" hidden="0" customHeight="1">
+      <x:c r="A65" s="20" t="str">
+        <x:v>P12</x:v>
+      </x:c>
+      <x:c r="B65" s="20" t="str">
+        <x:v>run_high</x:v>
+      </x:c>
+      <x:c r="C65" s="20" t="str">
+        <x:v>apple_watch</x:v>
+      </x:c>
+      <x:c r="D65" s="39" t="str">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E65" s="39" t="str">
+        <x:v>85.0</x:v>
+      </x:c>
+      <x:c r="F65" s="37" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="G65" s="37" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="H65" s="37" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="I65" s="37" t="str">
+        <x:v>-7.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="15" hidden="0" customHeight="1">
+      <x:c r="A66" s="57" t="str">
+        <x:v>P13</x:v>
+      </x:c>
+      <x:c r="B66" s="57" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C66" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D66" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E66" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F66" s="58" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="G66" s="58" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="H66" s="58" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="I66" s="58" t="str">
+        <x:v>6.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="15" hidden="0" customHeight="1">
+      <x:c r="A67" s="20" t="str">
+        <x:v>P13</x:v>
+      </x:c>
+      <x:c r="B67" s="20" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C67" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D67" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E67" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F67" s="37" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="G67" s="37" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="H67" s="37" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="I67" s="37" t="str">
+        <x:v>10.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="15" hidden="0" customHeight="1">
+      <x:c r="A68" s="57" t="str">
+        <x:v>P13</x:v>
+      </x:c>
+      <x:c r="B68" s="57" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C68" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D68" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E68" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F68" s="58" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="G68" s="58" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="H68" s="58" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="I68" s="58" t="str">
+        <x:v>13.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="15" hidden="0" customHeight="1">
+      <x:c r="A69" s="20" t="str">
+        <x:v>P13</x:v>
+      </x:c>
+      <x:c r="B69" s="20" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C69" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D69" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E69" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F69" s="37" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="G69" s="37" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="H69" s="37" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="I69" s="37" t="str">
+        <x:v>2.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="15" hidden="0" customHeight="1">
+      <x:c r="A70" s="57" t="str">
+        <x:v>P13</x:v>
+      </x:c>
+      <x:c r="B70" s="57" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C70" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D70" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E70" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F70" s="58" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="G70" s="58" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="H70" s="58" t="str">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="I70" s="58" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="15" hidden="0" customHeight="1">
+      <x:c r="A71" s="20" t="str">
+        <x:v>P14</x:v>
+      </x:c>
+      <x:c r="B71" s="20" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C71" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D71" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E71" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F71" s="37" t="str">
+        <x:v>0.438</x:v>
+      </x:c>
+      <x:c r="G71" s="37" t="str">
+        <x:v>0.438</x:v>
+      </x:c>
+      <x:c r="H71" s="37" t="str">
+        <x:v>0.438</x:v>
+      </x:c>
+      <x:c r="I71" s="37" t="str">
+        <x:v>10.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="15" hidden="0" customHeight="1">
+      <x:c r="A72" s="57" t="str">
+        <x:v>P14</x:v>
+      </x:c>
+      <x:c r="B72" s="57" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C72" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D72" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E72" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F72" s="58" t="str">
+        <x:v>0.438</x:v>
+      </x:c>
+      <x:c r="G72" s="58" t="str">
+        <x:v>0.438</x:v>
+      </x:c>
+      <x:c r="H72" s="58" t="str">
+        <x:v>0.438</x:v>
+      </x:c>
+      <x:c r="I72" s="58" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="15" hidden="0" customHeight="1">
+      <x:c r="A73" s="20" t="str">
+        <x:v>P15</x:v>
+      </x:c>
+      <x:c r="B73" s="20" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C73" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D73" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E73" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F73" s="37" t="str">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="G73" s="37" t="str">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="H73" s="37" t="str">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="I73" s="37" t="str">
+        <x:v>3.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="15" hidden="0" customHeight="1">
+      <x:c r="A74" s="57" t="str">
+        <x:v>P15</x:v>
+      </x:c>
+      <x:c r="B74" s="57" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C74" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D74" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E74" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F74" s="58" t="str">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="G74" s="58" t="str">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="H74" s="58" t="str">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="I74" s="58" t="str">
+        <x:v>5.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="15" hidden="0" customHeight="1">
+      <x:c r="A75" s="20" t="str">
+        <x:v>P15</x:v>
+      </x:c>
+      <x:c r="B75" s="20" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C75" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D75" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E75" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F75" s="37" t="str">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="G75" s="37" t="str">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="H75" s="37" t="str">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="I75" s="37" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="15" hidden="0" customHeight="1">
+      <x:c r="A76" s="57" t="str">
+        <x:v>P15</x:v>
+      </x:c>
+      <x:c r="B76" s="57" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C76" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D76" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E76" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F76" s="58" t="str">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="G76" s="58" t="str">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="H76" s="58" t="str">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="I76" s="58" t="str">
+        <x:v>15.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="15" hidden="0" customHeight="1">
+      <x:c r="A77" s="20" t="str">
+        <x:v>P16</x:v>
+      </x:c>
+      <x:c r="B77" s="20" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C77" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D77" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E77" s="39" t="str">
+        <x:v>88.33333333333333</x:v>
+      </x:c>
+      <x:c r="F77" s="37" t="str">
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="G77" s="37" t="str">
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="H77" s="37" t="str">
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="I77" s="37" t="str">
+        <x:v>11.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="15" hidden="0" customHeight="1">
+      <x:c r="A78" s="57" t="str">
+        <x:v>P16</x:v>
+      </x:c>
+      <x:c r="B78" s="57" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C78" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D78" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E78" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F78" s="58" t="str">
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="G78" s="58" t="str">
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="H78" s="58" t="str">
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="I78" s="58" t="str">
+        <x:v>5.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="15" hidden="0" customHeight="1">
+      <x:c r="A79" s="20" t="str">
+        <x:v>P16</x:v>
+      </x:c>
+      <x:c r="B79" s="20" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C79" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D79" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E79" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F79" s="37" t="str">
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="G79" s="37" t="str">
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="H79" s="37" t="str">
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="I79" s="37" t="str">
+        <x:v>-4.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="15" hidden="0" customHeight="1">
+      <x:c r="A80" s="57" t="str">
+        <x:v>P17</x:v>
+      </x:c>
+      <x:c r="B80" s="57" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="C80" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D80" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E80" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F80" s="58" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="G80" s="58" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="H80" s="58" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="I80" s="58" t="str">
+        <x:v>7.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="15" hidden="0" customHeight="1">
+      <x:c r="A81" s="20" t="str">
+        <x:v>P17</x:v>
+      </x:c>
+      <x:c r="B81" s="20" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="C81" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D81" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E81" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F81" s="37" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="G81" s="37" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="H81" s="37" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="I81" s="37" t="str">
+        <x:v>-2.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="15" hidden="0" customHeight="1">
+      <x:c r="A82" s="57" t="str">
+        <x:v>P17</x:v>
+      </x:c>
+      <x:c r="B82" s="57" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="C82" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D82" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E82" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F82" s="58" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="G82" s="58" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="H82" s="58" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="I82" s="58" t="str">
+        <x:v>3.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="15" hidden="0" customHeight="1">
+      <x:c r="A83" s="20" t="str">
+        <x:v>P17</x:v>
+      </x:c>
+      <x:c r="B83" s="20" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="C83" s="20" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D83" s="39" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E83" s="39" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F83" s="37" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="G83" s="37" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="H83" s="37" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="I83" s="37" t="str">
+        <x:v>14.0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="15" hidden="0" customHeight="1">
+      <x:c r="A84" s="57" t="str">
+        <x:v>P17</x:v>
+      </x:c>
+      <x:c r="B84" s="57" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="C84" s="57" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="D84" s="59" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E84" s="59" t="str">
+        <x:v>100.0</x:v>
+      </x:c>
+      <x:c r="F84" s="58" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="G84" s="58" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="H84" s="58" t="str">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="I84" s="58" t="str">
+        <x:v>-15.0</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="58" hidden="0" customHeight="1">
+      <x:c r="A1" s="54" t="str">
+        <x:v>analysis</x:v>
+      </x:c>
+      <x:c r="B1" s="55" t="str">
+        <x:v>tests</x:v>
+      </x:c>
+      <x:c r="C1" s="55" t="str">
+        <x:v>participants</x:v>
+      </x:c>
+      <x:c r="D1" s="55" t="str">
+        <x:v>base_mae</x:v>
+      </x:c>
+      <x:c r="E1" s="55" t="str">
+        <x:v>augmented_mae</x:v>
+      </x:c>
+      <x:c r="F1" s="55" t="str">
+        <x:v>mae_difference_augmented_minus_base</x:v>
+      </x:c>
+      <x:c r="G1" s="55" t="str">
+        <x:v>ci_low</x:v>
+      </x:c>
+      <x:c r="H1" s="55" t="str">
+        <x:v>ci_high</x:v>
+      </x:c>
+      <x:c r="I1" s="55" t="str">
+        <x:v>window_seconds</x:v>
+      </x:c>
+      <x:c r="J1" s="55" t="str">
+        <x:v>baseline_method</x:v>
+      </x:c>
+      <x:c r="K1" s="56" t="str">
+        <x:v>smoothing_seconds</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="57" t="str">
+        <x:v>recovery_60s__recovery_min__smooth_15s</x:v>
+      </x:c>
+      <x:c r="B2" s="59" t="str">
+        <x:v>757</x:v>
+      </x:c>
+      <x:c r="C2" s="59" t="str">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="D2" s="58" t="str">
+        <x:v>131.85437131218532</x:v>
+      </x:c>
+      <x:c r="E2" s="58" t="str">
+        <x:v>132.3642148441706</x:v>
+      </x:c>
+      <x:c r="F2" s="58" t="str">
+        <x:v>0.5098435319852878</x:v>
+      </x:c>
+      <x:c r="G2" s="58" t="str">
+        <x:v>0.17439134843185</x:v>
+      </x:c>
+      <x:c r="H2" s="58" t="str">
+        <x:v>0.8277382772073271</x:v>
+      </x:c>
+      <x:c r="I2" s="59" t="str">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J2" s="57" t="str">
+        <x:v>recovery_min</x:v>
+      </x:c>
+      <x:c r="K2" s="59" t="str">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="20" t="str">
+        <x:v>recovery_60s__recovery_final30_median__smooth_15s</x:v>
+      </x:c>
+      <x:c r="B3" s="39" t="str">
+        <x:v>757</x:v>
+      </x:c>
+      <x:c r="C3" s="39" t="str">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="D3" s="37" t="str">
+        <x:v>84.01452750110295</x:v>
+      </x:c>
+      <x:c r="E3" s="37" t="str">
+        <x:v>84.36761460871784</x:v>
+      </x:c>
+      <x:c r="F3" s="37" t="str">
+        <x:v>0.35308710761490214</x:v>
+      </x:c>
+      <x:c r="G3" s="37" t="str">
+        <x:v>-0.2174411937591004</x:v>
+      </x:c>
+      <x:c r="H3" s="37" t="str">
+        <x:v>0.9024172419569204</x:v>
+      </x:c>
+      <x:c r="I3" s="39" t="str">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J3" s="20" t="str">
+        <x:v>recovery_final30_median</x:v>
+      </x:c>
+      <x:c r="K3" s="39" t="str">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="57" t="str">
+        <x:v>recovery_60s__pre_effort_rolling30_min__smooth_15s</x:v>
+      </x:c>
+      <x:c r="B4" s="59" t="str">
+        <x:v>753</x:v>
+      </x:c>
+      <x:c r="C4" s="59" t="str">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="D4" s="58" t="str">
+        <x:v>261.3507508731592</x:v>
+      </x:c>
+      <x:c r="E4" s="58" t="str">
+        <x:v>261.8735368107437</x:v>
+      </x:c>
+      <x:c r="F4" s="58" t="str">
+        <x:v>0.522785937584491</x:v>
+      </x:c>
+      <x:c r="G4" s="58" t="str">
+        <x:v>-1.3437204327693972</x:v>
+      </x:c>
+      <x:c r="H4" s="58" t="str">
+        <x:v>2.469156070141015</x:v>
+      </x:c>
+      <x:c r="I4" s="59" t="str">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J4" s="57" t="str">
+        <x:v>pre_effort_rolling30_min</x:v>
+      </x:c>
+      <x:c r="K4" s="59" t="str">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="20" t="str">
+        <x:v>recovery_120s__recovery_min__smooth_15s</x:v>
+      </x:c>
+      <x:c r="B5" s="39" t="str">
+        <x:v>757</x:v>
+      </x:c>
+      <x:c r="C5" s="39" t="str">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="D5" s="37" t="str">
+        <x:v>272.8931433255874</x:v>
+      </x:c>
+      <x:c r="E5" s="37" t="str">
+        <x:v>272.3708059399274</x:v>
+      </x:c>
+      <x:c r="F5" s="37" t="str">
+        <x:v>-0.522337385660043</x:v>
+      </x:c>
+      <x:c r="G5" s="37" t="str">
+        <x:v>-2.0530090176148104</x:v>
+      </x:c>
+      <x:c r="H5" s="37" t="str">
+        <x:v>0.9534999050780553</x:v>
+      </x:c>
+      <x:c r="I5" s="39" t="str">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="J5" s="20" t="str">
+        <x:v>recovery_min</x:v>
+      </x:c>
+      <x:c r="K5" s="39" t="str">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="57" t="str">
+        <x:v>recovery_120s__recovery_final30_median__smooth_15s</x:v>
+      </x:c>
+      <x:c r="B6" s="59" t="str">
+        <x:v>757</x:v>
+      </x:c>
+      <x:c r="C6" s="59" t="str">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="D6" s="58" t="str">
+        <x:v>253.05497241348837</x:v>
+      </x:c>
+      <x:c r="E6" s="58" t="str">
+        <x:v>253.19609470824204</x:v>
+      </x:c>
+      <x:c r="F6" s="58" t="str">
+        <x:v>0.1411222947536142</x:v>
+      </x:c>
+      <x:c r="G6" s="58" t="str">
+        <x:v>-0.7765738406915325</x:v>
+      </x:c>
+      <x:c r="H6" s="58" t="str">
+        <x:v>1.1246644008095794</x:v>
+      </x:c>
+      <x:c r="I6" s="59" t="str">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="J6" s="57" t="str">
+        <x:v>recovery_final30_median</x:v>
+      </x:c>
+      <x:c r="K6" s="59" t="str">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="20" t="str">
+        <x:v>recovery_120s__pre_effort_rolling30_min__smooth_15s</x:v>
+      </x:c>
+      <x:c r="B7" s="39" t="str">
+        <x:v>753</x:v>
+      </x:c>
+      <x:c r="C7" s="39" t="str">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="D7" s="37" t="str">
+        <x:v>405.72304363409705</x:v>
+      </x:c>
+      <x:c r="E7" s="37" t="str">
+        <x:v>404.95201996929273</x:v>
+      </x:c>
+      <x:c r="F7" s="37" t="str">
+        <x:v>-0.77102366480437</x:v>
+      </x:c>
+      <x:c r="G7" s="37" t="str">
+        <x:v>-4.028977080814619</x:v>
+      </x:c>
+      <x:c r="H7" s="37" t="str">
+        <x:v>2.569367942317204</x:v>
+      </x:c>
+      <x:c r="I7" s="39" t="str">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="J7" s="20" t="str">
+        <x:v>pre_effort_rolling30_min</x:v>
+      </x:c>
+      <x:c r="K7" s="39" t="str">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="57" t="str">
+        <x:v>recovery_180s__recovery_min__smooth_15s</x:v>
+      </x:c>
+      <x:c r="B8" s="59" t="str">
+        <x:v>758</x:v>
+      </x:c>
+      <x:c r="C8" s="59" t="str">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="D8" s="58" t="str">
+        <x:v>347.4036561196649</x:v>
+      </x:c>
+      <x:c r="E8" s="58" t="str">
+        <x:v>347.4122011622173</x:v>
+      </x:c>
+      <x:c r="F8" s="58" t="str">
+        <x:v>0.00854504255241393</x:v>
+      </x:c>
+      <x:c r="G8" s="58" t="str">
+        <x:v>-1.2341171683245178</x:v>
+      </x:c>
+      <x:c r="H8" s="58" t="str">
+        <x:v>1.276084600830612</x:v>
+      </x:c>
+      <x:c r="I8" s="59" t="str">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="J8" s="57" t="str">
+        <x:v>recovery_min</x:v>
+      </x:c>
+      <x:c r="K8" s="59" t="str">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="20" t="str">
+        <x:v>recovery_180s__recovery_final30_median__smooth_15s</x:v>
+      </x:c>
+      <x:c r="B9" s="39" t="str">
+        <x:v>758</x:v>
+      </x:c>
+      <x:c r="C9" s="39" t="str">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="D9" s="37" t="str">
+        <x:v>320.5801639374397</x:v>
+      </x:c>
+      <x:c r="E9" s="37" t="str">
+        <x:v>320.92661310530923</x:v>
+      </x:c>
+      <x:c r="F9" s="37" t="str">
+        <x:v>0.34644916786951385</x:v>
+      </x:c>
+      <x:c r="G9" s="37" t="str">
+        <x:v>-1.1965332834363842</x:v>
+      </x:c>
+      <x:c r="H9" s="37" t="str">
+        <x:v>1.9369470078839492</x:v>
+      </x:c>
+      <x:c r="I9" s="39" t="str">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="J9" s="20" t="str">
+        <x:v>recovery_final30_median</x:v>
+      </x:c>
+      <x:c r="K9" s="39" t="str">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="57" t="str">
+        <x:v>recovery_180s__pre_effort_rolling30_min__smooth_15s</x:v>
+      </x:c>
+      <x:c r="B10" s="59" t="str">
+        <x:v>754</x:v>
+      </x:c>
+      <x:c r="C10" s="59" t="str">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="D10" s="58" t="str">
+        <x:v>510.5662379669843</x:v>
+      </x:c>
+      <x:c r="E10" s="58" t="str">
+        <x:v>510.25589155220257</x:v>
+      </x:c>
+      <x:c r="F10" s="58" t="str">
+        <x:v>-0.31034641478170283</x:v>
+      </x:c>
+      <x:c r="G10" s="58" t="str">
+        <x:v>-4.516882934382165</x:v>
+      </x:c>
+      <x:c r="H10" s="58" t="str">
+        <x:v>3.920681435658158</x:v>
+      </x:c>
+      <x:c r="I10" s="59" t="str">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="J10" s="57" t="str">
+        <x:v>pre_effort_rolling30_min</x:v>
+      </x:c>
+      <x:c r="K10" s="59" t="str">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="20" t="str">
+        <x:v>recovery_180s__recovery_final30_median__smooth_5s</x:v>
+      </x:c>
+      <x:c r="B11" s="39" t="str">
+        <x:v>758</x:v>
+      </x:c>
+      <x:c r="C11" s="39" t="str">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="D11" s="37" t="str">
+        <x:v>304.17430091761275</x:v>
+      </x:c>
+      <x:c r="E11" s="37" t="str">
+        <x:v>304.4431658340048</x:v>
+      </x:c>
+      <x:c r="F11" s="37" t="str">
+        <x:v>0.2688649163921074</x:v>
+      </x:c>
+      <x:c r="G11" s="37" t="str">
+        <x:v>-1.18577865592953</x:v>
+      </x:c>
+      <x:c r="H11" s="37" t="str">
+        <x:v>1.8213861030485483</x:v>
+      </x:c>
+      <x:c r="I11" s="39" t="str">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="J11" s="20" t="str">
+        <x:v>recovery_final30_median</x:v>
+      </x:c>
+      <x:c r="K11" s="39" t="str">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="57" t="str">
+        <x:v>recovery_180s__recovery_final30_median__smooth_30s</x:v>
+      </x:c>
+      <x:c r="B12" s="59" t="str">
+        <x:v>758</x:v>
+      </x:c>
+      <x:c r="C12" s="59" t="str">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="D12" s="58" t="str">
+        <x:v>329.36951051309467</x:v>
+      </x:c>
+      <x:c r="E12" s="58" t="str">
+        <x:v>330.2571674871837</x:v>
+      </x:c>
+      <x:c r="F12" s="58" t="str">
+        <x:v>0.8876569740889795</x:v>
+      </x:c>
+      <x:c r="G12" s="58" t="str">
+        <x:v>-1.1491692050370628</x:v>
+      </x:c>
+      <x:c r="H12" s="58" t="str">
+        <x:v>2.982682916113159</x:v>
+      </x:c>
+      <x:c r="I12" s="59" t="str">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="J12" s="57" t="str">
+        <x:v>recovery_final30_median</x:v>
+      </x:c>
+      <x:c r="K12" s="59" t="str">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="58" hidden="0" customHeight="1">
+      <x:c r="A1" s="54" t="str">
+        <x:v>analysis</x:v>
+      </x:c>
+      <x:c r="B1" s="55" t="str">
+        <x:v>tests</x:v>
+      </x:c>
+      <x:c r="C1" s="55" t="str">
+        <x:v>participants</x:v>
+      </x:c>
+      <x:c r="D1" s="55" t="str">
+        <x:v>base_mae</x:v>
+      </x:c>
+      <x:c r="E1" s="55" t="str">
+        <x:v>augmented_mae</x:v>
+      </x:c>
+      <x:c r="F1" s="55" t="str">
+        <x:v>mae_difference_augmented_minus_base</x:v>
+      </x:c>
+      <x:c r="G1" s="55" t="str">
+        <x:v>ci_low</x:v>
+      </x:c>
+      <x:c r="H1" s="55" t="str">
+        <x:v>ci_high</x:v>
+      </x:c>
+      <x:c r="I1" s="56" t="str">
+        <x:v>hr_anchor_method</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="57" t="str">
+        <x:v>hr_lower_anchor__pre_rolling30_min</x:v>
+      </x:c>
+      <x:c r="B2" s="59" t="str">
+        <x:v>758</x:v>
+      </x:c>
+      <x:c r="C2" s="59" t="str">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="D2" s="58" t="str">
+        <x:v>347.40365611966496</x:v>
+      </x:c>
+      <x:c r="E2" s="58" t="str">
+        <x:v>347.4122011622174</x:v>
+      </x:c>
+      <x:c r="F2" s="58" t="str">
+        <x:v>0.008545042552434906</x:v>
+      </x:c>
+      <x:c r="G2" s="58" t="str">
+        <x:v>-1.234117168324471</x:v>
+      </x:c>
+      <x:c r="H2" s="58" t="str">
+        <x:v>1.2760846008306628</x:v>
+      </x:c>
+      <x:c r="I2" s="57" t="str">
+        <x:v>pre_rolling30_min</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="20" t="str">
+        <x:v>hr_lower_anchor__first60_median</x:v>
+      </x:c>
+      <x:c r="B3" s="39" t="str">
+        <x:v>758</x:v>
+      </x:c>
+      <x:c r="C3" s="39" t="str">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="D3" s="37" t="str">
+        <x:v>347.06161643331467</x:v>
+      </x:c>
+      <x:c r="E3" s="37" t="str">
+        <x:v>347.10492594466507</x:v>
+      </x:c>
+      <x:c r="F3" s="37" t="str">
+        <x:v>0.04330951135033109</x:v>
+      </x:c>
+      <x:c r="G3" s="37" t="str">
+        <x:v>-1.5697331695090717</x:v>
+      </x:c>
+      <x:c r="H3" s="37" t="str">
+        <x:v>1.7074287215757278</x:v>
+      </x:c>
+      <x:c r="I3" s="20" t="str">
+        <x:v>first60_median</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="57" t="str">
+        <x:v>hr_lower_anchor__pre_median</x:v>
+      </x:c>
+      <x:c r="B4" s="59" t="str">
+        <x:v>758</x:v>
+      </x:c>
+      <x:c r="C4" s="59" t="str">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="D4" s="58" t="str">
+        <x:v>346.989787393231</x:v>
+      </x:c>
+      <x:c r="E4" s="58" t="str">
+        <x:v>347.0953744013238</x:v>
+      </x:c>
+      <x:c r="F4" s="58" t="str">
+        <x:v>0.10558700809279985</x:v>
+      </x:c>
+      <x:c r="G4" s="58" t="str">
+        <x:v>-1.0365983216778891</x:v>
+      </x:c>
+      <x:c r="H4" s="58" t="str">
+        <x:v>1.3045960888816885</x:v>
+      </x:c>
+      <x:c r="I4" s="57" t="str">
+        <x:v>pre_median</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/results/tables/tHRR-I_public_data_results.xlsx
+++ b/results/tables/tHRR-I_public_data_results.xlsx
@@ -2,34 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rde40f86ed25a43a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prediction performance" sheetId="2" r:id="R3c612935666c4964"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prediction comparisons" sheetId="3" r:id="Rfa20b8268a2e4269"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Within-person summary" sheetId="4" r:id="Rd43c2d9230364a69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participant associations" sheetId="5" r:id="Ree9b0008790348f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discretization" sheetId="6" r:id="R30725bc87e174aa5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repeated splits summary" sheetId="7" r:id="R83932f81b2ac4fbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repeated splits" sheetId="8" r:id="R197199db3bb14607"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matching stability" sheetId="9" r:id="R7164591f809441e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High RPE balanced" sheetId="10" r:id="R76245abdc79e4006"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High RPE participant" sheetId="11" r:id="Rf7dcd64dedeb4e59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ordinal sensitivity" sheetId="12" r:id="R9e576224f9cf491c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HRR clipping" sheetId="13" r:id="R2d862d0bb17c40d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prediction range" sheetId="14" r:id="R31b3e2b568994afe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equal-mean examples" sheetId="15" r:id="R7d379f069b0b462b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw signal anchors" sheetId="16" r:id="R0447b8908c6e4530"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matching model performance" sheetId="17" r:id="R24b5e2b4937c43c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weight profile" sheetId="18" r:id="R9f612ae7e99144c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participant anchors" sheetId="19" r:id="R957c16fa2eca4c87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selection aware" sheetId="20" r:id="R6847d934b20d4aff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matching confidence" sheetId="21" r:id="R5d8f46733fde4d86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lambda heterogeneity" sheetId="22" r:id="Rcb48ec60a0b04dd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEE repeated measures" sheetId="23" r:id="Rf640f6b88e0f4fbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEE agreement" sheetId="24" r:id="Rbf2d5df6188d4264"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEE agreement intervals" sheetId="25" r:id="Rc2e075705c184385"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEE synchronization" sheetId="26" r:id="Rf2a81f0554064dc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Malaga endpoint sensitivity" sheetId="27" r:id="R52a2202dcfee426a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Malaga anchor sensitivity" sheetId="28" r:id="Re1b0523768b74030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0370997591664146"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prediction performance" sheetId="2" r:id="Rc271e24dd2e141af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prediction comparisons" sheetId="3" r:id="R7d76022ae85c42b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Within-person summary" sheetId="4" r:id="R2fbea52212a6451f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participant associations" sheetId="5" r:id="R7e1532104b98410c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discretization" sheetId="6" r:id="Rf65fc2fba687410e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repeated splits summary" sheetId="7" r:id="R230b9996939e4644"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repeated splits" sheetId="8" r:id="R81fde0cd68e0444d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matching stability" sheetId="9" r:id="Rd9152d637f4e4aea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High RPE balanced" sheetId="10" r:id="R6360094dd31145cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High RPE participant" sheetId="11" r:id="R8179f10258994c3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ordinal sensitivity" sheetId="12" r:id="Rfcb154cc1e1b41c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HRR clipping" sheetId="13" r:id="R443d2dda25534a2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prediction range" sheetId="14" r:id="Rc767f6481a9f4752"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equal-mean examples" sheetId="15" r:id="R09b3cf5fdbb74af6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw signal anchors" sheetId="16" r:id="Rd745448066304e2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matching model performance" sheetId="17" r:id="R197f680c70514c5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weight profile" sheetId="18" r:id="Rbe2ae7ffac654985"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participant anchors" sheetId="19" r:id="R740135567b53422d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selection aware" sheetId="20" r:id="Ra21be65c5e594c24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matching confidence" sheetId="21" r:id="Rc5306615c86948b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lambda heterogeneity" sheetId="22" r:id="R8ce05eaca8464e4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEE repeated measures" sheetId="23" r:id="R30a1d8554b2944b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEE agreement" sheetId="24" r:id="R9ee5eda159a946e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEE agreement intervals" sheetId="25" r:id="R3c04724d05714778"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEE synchronization" sheetId="26" r:id="R79630916f86f4640"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Malaga endpoint sensitivity" sheetId="27" r:id="R4a5b98e5a3e940e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Malaga anchor sensitivity" sheetId="28" r:id="Rd0f710fe6153406b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Round5_Incremental" sheetId="29" r:id="R362e557402824000"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Round5_ParticipantLoss" sheetId="30" r:id="R1cdb510d42084322"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Round5_SampleFlow" sheetId="31" r:id="R23ce3313cab549c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEE_RM_Agreement" sheetId="32" r:id="R90ed404f4c9446a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEE_StageFlow" sheetId="33" r:id="R93c425a859e54f4a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -40,11 +45,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="164" formatCode="0.0000"/>
     <x:numFmt numFmtId="200" formatCode="0"/>
+    <x:numFmt numFmtId="201" formatCode="0.000"/>
+    <x:numFmt numFmtId="202" formatCode="0.0"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -75,8 +82,43 @@
       <x:color rgb="FF007C91"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="15"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="8"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -113,8 +155,28 @@
         <x:fgColor rgb="FFEAF3F6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F6B78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEFEF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="4">
+  <x:borders count="5">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -146,11 +208,25 @@
         <x:color rgb="FF1E3F66"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB7C9D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB7C9D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB7C9D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB7C9D6"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="66">
+  <x:cellXfs count="83">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -311,6 +387,35 @@
     <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -635,7 +740,7 @@
         <x:v>Development status</x:v>
       </x:c>
       <x:c r="B4" s="64" t="str">
-        <x:v>Exploratory PMData method development; principal comparison was not preregistered</x:v>
+        <x:v>Exploratory PMData formula development; the round-5 outer-fold comparison was not preregistered</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -643,7 +748,7 @@
         <x:v>Selection-aware result</x:v>
       </x:c>
       <x:c r="B5" s="41" t="str">
-        <x:v>Outer LOPO reselected family and parameter: ΔMAE -0.094 RPE units (95% CI -0.161 to -0.031)</x:v>
+        <x:v>Mean HRR + Δtilt versus mean HRR: ΔMAE -0.070 RPE units (-0.165 to 0.035); exact P=0.228</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -683,7 +788,7 @@
         <x:v>Zephyr agreement</x:v>
       </x:c>
       <x:c r="B10" s="64" t="str">
-        <x:v>tHRR-I ICC(A,1) 0.854 (0.667 to 0.952); limits of agreement -0.257 to 0.205</x:v>
+        <x:v>Zephyr tHRR-I participant-balanced CCC 0.846 (0.654 to 0.946); repeated-measures limits -0.262 to 0.213</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -699,7 +804,7 @@
         <x:v>Practical interpretation</x:v>
       </x:c>
       <x:c r="B12" s="64" t="str">
-        <x:v>Candidate retrospective session-review descriptor; not a prescription, alert, or clinical measure</x:v>
+        <x:v>Research-level retrospective session descriptor; not a prescription, alert, or clinical measure</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -707,7 +812,7 @@
         <x:v>Uncertainty</x:v>
       </x:c>
       <x:c r="B13" s="41" t="str">
-        <x:v>Participant-cluster intervals; formula-invention optimism remains in PMData</x:v>
+        <x:v>Participant-cluster intervals; model-family invention and fixed-λ sensitivities remain development-sample conditional</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -723,7 +828,7 @@
         <x:v>Software</x:v>
       </x:c>
       <x:c r="B15" s="41" t="str">
-        <x:v>Python 3.12.13; pandas 2.2.3; NumPy 2.3.5; openpyxl 3.1.5</x:v>
+        <x:v>Analysis: Python 3.12.13, pandas 2.2.3, NumPy 2.3.5; workbook assembly: @oai/artifact-tool 2.8.6+</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8204,6 +8309,450 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="29" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="67" t="str">
+        <x:v>Round 5: participant-grouped model comparison</x:v>
+      </x:c>
+      <x:c r="B1" s="67" t="str">
+        <x:v>Round 5: participant-grouped model comparison</x:v>
+      </x:c>
+      <x:c r="C1" s="67" t="str">
+        <x:v>Round 5: participant-grouped model comparison</x:v>
+      </x:c>
+      <x:c r="D1" s="67" t="str">
+        <x:v>Round 5: participant-grouped model comparison</x:v>
+      </x:c>
+      <x:c r="E1" s="67" t="str">
+        <x:v>Round 5: participant-grouped model comparison</x:v>
+      </x:c>
+      <x:c r="F1" s="67" t="str">
+        <x:v>Round 5: participant-grouped model comparison</x:v>
+      </x:c>
+      <x:c r="G1" s="67" t="str">
+        <x:v>Round 5: participant-grouped model comparison</x:v>
+      </x:c>
+      <x:c r="H1" s="67" t="str">
+        <x:v>Round 5: participant-grouped model comparison</x:v>
+      </x:c>
+      <x:c r="I1" s="67" t="str">
+        <x:v>Round 5: participant-grouped model comparison</x:v>
+      </x:c>
+      <x:c r="J1" s="67" t="str">
+        <x:v>Round 5: participant-grouped model comparison</x:v>
+      </x:c>
+      <x:c r="K1" s="67" t="str">
+        <x:v>Round 5: participant-grouped model comparison</x:v>
+      </x:c>
+      <x:c r="L1" s="67" t="str">
+        <x:v>Round 5: participant-grouped model comparison</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="70" t="str">
+        <x:v>Negative ΔMAE favors the candidate. Participant is the independent resampling unit. Fixed-λ rows are development-condition sensitivities.</x:v>
+      </x:c>
+      <x:c r="B2" s="70" t="str">
+        <x:v>Negative ΔMAE favors the candidate. Participant is the independent resampling unit. Fixed-λ rows are development-condition sensitivities.</x:v>
+      </x:c>
+      <x:c r="C2" s="70" t="str">
+        <x:v>Negative ΔMAE favors the candidate. Participant is the independent resampling unit. Fixed-λ rows are development-condition sensitivities.</x:v>
+      </x:c>
+      <x:c r="D2" s="70" t="str">
+        <x:v>Negative ΔMAE favors the candidate. Participant is the independent resampling unit. Fixed-λ rows are development-condition sensitivities.</x:v>
+      </x:c>
+      <x:c r="E2" s="70" t="str">
+        <x:v>Negative ΔMAE favors the candidate. Participant is the independent resampling unit. Fixed-λ rows are development-condition sensitivities.</x:v>
+      </x:c>
+      <x:c r="F2" s="70" t="str">
+        <x:v>Negative ΔMAE favors the candidate. Participant is the independent resampling unit. Fixed-λ rows are development-condition sensitivities.</x:v>
+      </x:c>
+      <x:c r="G2" s="70" t="str">
+        <x:v>Negative ΔMAE favors the candidate. Participant is the independent resampling unit. Fixed-λ rows are development-condition sensitivities.</x:v>
+      </x:c>
+      <x:c r="H2" s="70" t="str">
+        <x:v>Negative ΔMAE favors the candidate. Participant is the independent resampling unit. Fixed-λ rows are development-condition sensitivities.</x:v>
+      </x:c>
+      <x:c r="I2" s="70" t="str">
+        <x:v>Negative ΔMAE favors the candidate. Participant is the independent resampling unit. Fixed-λ rows are development-condition sensitivities.</x:v>
+      </x:c>
+      <x:c r="J2" s="70" t="str">
+        <x:v>Negative ΔMAE favors the candidate. Participant is the independent resampling unit. Fixed-λ rows are development-condition sensitivities.</x:v>
+      </x:c>
+      <x:c r="K2" s="70" t="str">
+        <x:v>Negative ΔMAE favors the candidate. Participant is the independent resampling unit. Fixed-λ rows are development-condition sensitivities.</x:v>
+      </x:c>
+      <x:c r="L2" s="70" t="str">
+        <x:v>Negative ΔMAE favors the candidate. Participant is the independent resampling unit. Fixed-λ rows are development-condition sensitivities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="75" t="str">
+        <x:v>Model</x:v>
+      </x:c>
+      <x:c r="B4" s="75" t="str">
+        <x:v>Participants</x:v>
+      </x:c>
+      <x:c r="C4" s="75" t="str">
+        <x:v>Participant-balanced MAE</x:v>
+      </x:c>
+      <x:c r="D4" s="75" t="str">
+        <x:v>ΔMAE vs mean HRR</x:v>
+      </x:c>
+      <x:c r="E4" s="75" t="str">
+        <x:v>Relative MAE change (%)</x:v>
+      </x:c>
+      <x:c r="F4" s="75" t="str">
+        <x:v>Bootstrap lower</x:v>
+      </x:c>
+      <x:c r="G4" s="75" t="str">
+        <x:v>Bootstrap upper</x:v>
+      </x:c>
+      <x:c r="H4" s="75" t="str">
+        <x:v>Exact sign-flip P</x:v>
+      </x:c>
+      <x:c r="I4" s="75" t="str">
+        <x:v>Favor candidate (n)</x:v>
+      </x:c>
+      <x:c r="J4" s="75" t="str">
+        <x:v>Favor base (n)</x:v>
+      </x:c>
+      <x:c r="K4" s="75" t="str">
+        <x:v>Leave-one-out Δ min</x:v>
+      </x:c>
+      <x:c r="L4" s="75" t="str">
+        <x:v>Leave-one-out Δ max</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="76" t="str">
+        <x:v>Mean HRR</x:v>
+      </x:c>
+      <x:c r="B5" s="76" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C5" s="77" t="n">
+        <x:v>1.3020464195357122</x:v>
+      </x:c>
+      <x:c r="D5" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E5" s="78" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F5" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="77"/>
+      <x:c r="I5" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J5" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K5" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L5" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="76" t="str">
+        <x:v>Mean HRR + variance</x:v>
+      </x:c>
+      <x:c r="B6" s="76" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C6" s="77" t="n">
+        <x:v>1.2937751659446943</x:v>
+      </x:c>
+      <x:c r="D6" s="77" t="n">
+        <x:v>-0.008271253591017621</x:v>
+      </x:c>
+      <x:c r="E6" s="78" t="n">
+        <x:v>-0.6352502850065062</x:v>
+      </x:c>
+      <x:c r="F6" s="77" t="n">
+        <x:v>-0.0640127908795715</x:v>
+      </x:c>
+      <x:c r="G6" s="77" t="n">
+        <x:v>0.05372513314046594</x:v>
+      </x:c>
+      <x:c r="H6" s="77" t="n">
+        <x:v>0.798095703125</x:v>
+      </x:c>
+      <x:c r="I6" s="77" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J6" s="77" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K6" s="77" t="n">
+        <x:v>-0.02867709835210867</x:v>
+      </x:c>
+      <x:c r="L6" s="77" t="n">
+        <x:v>0.00488033152080007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="76" t="str">
+        <x:v>Mean HRR + time ≥80% HRR</x:v>
+      </x:c>
+      <x:c r="B7" s="76" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C7" s="77" t="n">
+        <x:v>1.2789399577902902</x:v>
+      </x:c>
+      <x:c r="D7" s="77" t="n">
+        <x:v>-0.023106461745421726</x:v>
+      </x:c>
+      <x:c r="E7" s="78" t="n">
+        <x:v>-1.7746265723507078</x:v>
+      </x:c>
+      <x:c r="F7" s="77" t="n">
+        <x:v>-0.13557657143293464</x:v>
+      </x:c>
+      <x:c r="G7" s="77" t="n">
+        <x:v>0.10695448726255276</x:v>
+      </x:c>
+      <x:c r="H7" s="77" t="n">
+        <x:v>0.7205810546875</x:v>
+      </x:c>
+      <x:c r="I7" s="77" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="77" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K7" s="77" t="n">
+        <x:v>-0.05758196383070456</x:v>
+      </x:c>
+      <x:c r="L7" s="77" t="n">
+        <x:v>-0.00044134386031396966</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="76" t="str">
+        <x:v>Mean HRR + Δtilt, fixed λ=6.2</x:v>
+      </x:c>
+      <x:c r="B8" s="76" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C8" s="77" t="n">
+        <x:v>1.2282576049993592</x:v>
+      </x:c>
+      <x:c r="D8" s="77" t="n">
+        <x:v>-0.0737888145363529</x:v>
+      </x:c>
+      <x:c r="E8" s="78" t="n">
+        <x:v>-5.667141618703943</x:v>
+      </x:c>
+      <x:c r="F8" s="77" t="n">
+        <x:v>-0.15494498038670443</x:v>
+      </x:c>
+      <x:c r="G8" s="77" t="n">
+        <x:v>0.0017989210274185934</x:v>
+      </x:c>
+      <x:c r="H8" s="77" t="n">
+        <x:v>0.09844970703125</x:v>
+      </x:c>
+      <x:c r="I8" s="77" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J8" s="77" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K8" s="77" t="n">
+        <x:v>-0.09104035335025747</x:v>
+      </x:c>
+      <x:c r="L8" s="77" t="n">
+        <x:v>-0.04984219599314725</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="76" t="str">
+        <x:v>tHRR-I alone, fixed λ=6.2</x:v>
+      </x:c>
+      <x:c r="B9" s="76" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="77" t="n">
+        <x:v>1.2276748933553887</x:v>
+      </x:c>
+      <x:c r="D9" s="77" t="n">
+        <x:v>-0.07437152618032332</x:v>
+      </x:c>
+      <x:c r="E9" s="78" t="n">
+        <x:v>-5.7118951417141455</x:v>
+      </x:c>
+      <x:c r="F9" s="77" t="n">
+        <x:v>-0.13308062840882492</x:v>
+      </x:c>
+      <x:c r="G9" s="77" t="n">
+        <x:v>-0.0171698191090123</x:v>
+      </x:c>
+      <x:c r="H9" s="77" t="n">
+        <x:v>0.02996826171875</x:v>
+      </x:c>
+      <x:c r="I9" s="77" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J9" s="77" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K9" s="77" t="n">
+        <x:v>-0.08466746313466</x:v>
+      </x:c>
+      <x:c r="L9" s="77" t="n">
+        <x:v>-0.059995828595085725</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="76" t="str">
+        <x:v>Mean HRR + Δtilt, nested λ</x:v>
+      </x:c>
+      <x:c r="B10" s="76" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="77" t="n">
+        <x:v>1.2320967470002568</x:v>
+      </x:c>
+      <x:c r="D10" s="77" t="n">
+        <x:v>-0.0699496725354552</x:v>
+      </x:c>
+      <x:c r="E10" s="78" t="n">
+        <x:v>-5.372287153970906</x:v>
+      </x:c>
+      <x:c r="F10" s="77" t="n">
+        <x:v>-0.16544334872389313</x:v>
+      </x:c>
+      <x:c r="G10" s="77" t="n">
+        <x:v>0.03487836821016581</x:v>
+      </x:c>
+      <x:c r="H10" s="77" t="n">
+        <x:v>0.2275390625</x:v>
+      </x:c>
+      <x:c r="I10" s="77" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J10" s="77" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K10" s="77" t="n">
+        <x:v>-0.10906895743010171</x:v>
+      </x:c>
+      <x:c r="L10" s="77" t="n">
+        <x:v>-0.04511976036274091</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="76" t="str">
+        <x:v>Selection-aware transparent pipeline</x:v>
+      </x:c>
+      <x:c r="B11" s="76" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="77" t="n">
+        <x:v>1.2449495567696305</x:v>
+      </x:c>
+      <x:c r="D11" s="77" t="n">
+        <x:v>-0.057096862766081495</x:v>
+      </x:c>
+      <x:c r="E11" s="78" t="n">
+        <x:v>-4.385163378924791</x:v>
+      </x:c>
+      <x:c r="F11" s="77" t="n">
+        <x:v>-0.15098765691397598</x:v>
+      </x:c>
+      <x:c r="G11" s="77" t="n">
+        <x:v>0.04824985027560582</x:v>
+      </x:c>
+      <x:c r="H11" s="77" t="n">
+        <x:v>0.3115234375</x:v>
+      </x:c>
+      <x:c r="I11" s="77" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J11" s="77" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K11" s="77" t="n">
+        <x:v>-0.09529808982005845</x:v>
+      </x:c>
+      <x:c r="L11" s="77" t="n">
+        <x:v>-0.031348892752697644</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="34" customHeight="1">
+      <x:c r="A13" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_model_performance.csv | Public data: https://datasets.simula.no/pmdata/</x:v>
+      </x:c>
+      <x:c r="B13" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_model_performance.csv | Public data: https://datasets.simula.no/pmdata/</x:v>
+      </x:c>
+      <x:c r="C13" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_model_performance.csv | Public data: https://datasets.simula.no/pmdata/</x:v>
+      </x:c>
+      <x:c r="D13" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_model_performance.csv | Public data: https://datasets.simula.no/pmdata/</x:v>
+      </x:c>
+      <x:c r="E13" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_model_performance.csv | Public data: https://datasets.simula.no/pmdata/</x:v>
+      </x:c>
+      <x:c r="F13" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_model_performance.csv | Public data: https://datasets.simula.no/pmdata/</x:v>
+      </x:c>
+      <x:c r="G13" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_model_performance.csv | Public data: https://datasets.simula.no/pmdata/</x:v>
+      </x:c>
+      <x:c r="H13" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_model_performance.csv | Public data: https://datasets.simula.no/pmdata/</x:v>
+      </x:c>
+      <x:c r="I13" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_model_performance.csv | Public data: https://datasets.simula.no/pmdata/</x:v>
+      </x:c>
+      <x:c r="J13" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_model_performance.csv | Public data: https://datasets.simula.no/pmdata/</x:v>
+      </x:c>
+      <x:c r="K13" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_model_performance.csv | Public data: https://datasets.simula.no/pmdata/</x:v>
+      </x:c>
+      <x:c r="L13" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_model_performance.csv | Public data: https://datasets.simula.no/pmdata/</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:L1"/>
+    <x:mergeCell ref="A2:L2"/>
+    <x:mergeCell ref="A13:L13"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8537,6 +9086,2071 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="67" t="str">
+        <x:v>Participant-level held-out losses</x:v>
+      </x:c>
+      <x:c r="B1" s="67" t="str">
+        <x:v>Participant-level held-out losses</x:v>
+      </x:c>
+      <x:c r="C1" s="67" t="str">
+        <x:v>Participant-level held-out losses</x:v>
+      </x:c>
+      <x:c r="D1" s="67" t="str">
+        <x:v>Participant-level held-out losses</x:v>
+      </x:c>
+      <x:c r="E1" s="67" t="str">
+        <x:v>Participant-level held-out losses</x:v>
+      </x:c>
+      <x:c r="F1" s="67" t="str">
+        <x:v>Participant-level held-out losses</x:v>
+      </x:c>
+      <x:c r="G1" s="67" t="str">
+        <x:v>Participant-level held-out losses</x:v>
+      </x:c>
+      <x:c r="H1" s="67" t="str">
+        <x:v>Participant-level held-out losses</x:v>
+      </x:c>
+      <x:c r="I1" s="67" t="str">
+        <x:v>Participant-level held-out losses</x:v>
+      </x:c>
+      <x:c r="J1" s="67" t="str">
+        <x:v>Participant-level held-out losses</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="70" t="str">
+        <x:v>Formulas calculate paired ΔMAE from the archived participant-level MAE columns; negative values favor the candidate.</x:v>
+      </x:c>
+      <x:c r="B2" s="70" t="str">
+        <x:v>Formulas calculate paired ΔMAE from the archived participant-level MAE columns; negative values favor the candidate.</x:v>
+      </x:c>
+      <x:c r="C2" s="70" t="str">
+        <x:v>Formulas calculate paired ΔMAE from the archived participant-level MAE columns; negative values favor the candidate.</x:v>
+      </x:c>
+      <x:c r="D2" s="70" t="str">
+        <x:v>Formulas calculate paired ΔMAE from the archived participant-level MAE columns; negative values favor the candidate.</x:v>
+      </x:c>
+      <x:c r="E2" s="70" t="str">
+        <x:v>Formulas calculate paired ΔMAE from the archived participant-level MAE columns; negative values favor the candidate.</x:v>
+      </x:c>
+      <x:c r="F2" s="70" t="str">
+        <x:v>Formulas calculate paired ΔMAE from the archived participant-level MAE columns; negative values favor the candidate.</x:v>
+      </x:c>
+      <x:c r="G2" s="70" t="str">
+        <x:v>Formulas calculate paired ΔMAE from the archived participant-level MAE columns; negative values favor the candidate.</x:v>
+      </x:c>
+      <x:c r="H2" s="70" t="str">
+        <x:v>Formulas calculate paired ΔMAE from the archived participant-level MAE columns; negative values favor the candidate.</x:v>
+      </x:c>
+      <x:c r="I2" s="70" t="str">
+        <x:v>Formulas calculate paired ΔMAE from the archived participant-level MAE columns; negative values favor the candidate.</x:v>
+      </x:c>
+      <x:c r="J2" s="70" t="str">
+        <x:v>Formulas calculate paired ΔMAE from the archived participant-level MAE columns; negative values favor the candidate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="75" t="str">
+        <x:v>Participant</x:v>
+      </x:c>
+      <x:c r="B4" s="75" t="str">
+        <x:v>Sessions</x:v>
+      </x:c>
+      <x:c r="C4" s="75" t="str">
+        <x:v>Base mean MAE</x:v>
+      </x:c>
+      <x:c r="D4" s="75" t="str">
+        <x:v>Nested Δtilt MAE</x:v>
+      </x:c>
+      <x:c r="E4" s="75" t="str">
+        <x:v>ΔMAE nested</x:v>
+      </x:c>
+      <x:c r="F4" s="75" t="str">
+        <x:v>Fixed Δtilt MAE</x:v>
+      </x:c>
+      <x:c r="G4" s="75" t="str">
+        <x:v>ΔMAE fixed</x:v>
+      </x:c>
+      <x:c r="H4" s="75" t="str">
+        <x:v>Fixed tHRR-I MAE</x:v>
+      </x:c>
+      <x:c r="I4" s="75" t="str">
+        <x:v>ΔMAE stand-alone</x:v>
+      </x:c>
+      <x:c r="J4" s="75" t="str">
+        <x:v>Selected transparent MAE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="76" t="str">
+        <x:v>p01</x:v>
+      </x:c>
+      <x:c r="B5" s="76" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C5" s="77" t="n">
+        <x:v>0.6219671675554482</x:v>
+      </x:c>
+      <x:c r="D5" s="77" t="n">
+        <x:v>0.5575996125165622</x:v>
+      </x:c>
+      <x:c r="E5" s="77" t="n">
+        <x:f>D5-C5</x:f>
+        <x:v>-0.06436755503888603</x:v>
+      </x:c>
+      <x:c r="F5" s="77" t="n">
+        <x:v>0.5698426734342089</x:v>
+      </x:c>
+      <x:c r="G5" s="77" t="n">
+        <x:f>F5-C5</x:f>
+        <x:v>-0.05212449412123932</x:v>
+      </x:c>
+      <x:c r="H5" s="77" t="n">
+        <x:v>0.5612905339169952</x:v>
+      </x:c>
+      <x:c r="I5" s="77" t="n">
+        <x:f>H5-C5</x:f>
+        <x:v>-0.06067663363845299</x:v>
+      </x:c>
+      <x:c r="J5" s="77" t="n">
+        <x:v>0.5575996125165622</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="76" t="str">
+        <x:v>p02</x:v>
+      </x:c>
+      <x:c r="B6" s="76" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C6" s="77" t="n">
+        <x:v>0.655198327516322</x:v>
+      </x:c>
+      <x:c r="D6" s="77" t="n">
+        <x:v>0.6447678662943364</x:v>
+      </x:c>
+      <x:c r="E6" s="77" t="n">
+        <x:f>D6-C6</x:f>
+        <x:v>-0.010430461221985654</x:v>
+      </x:c>
+      <x:c r="F6" s="77" t="n">
+        <x:v>0.680294520303867</x:v>
+      </x:c>
+      <x:c r="G6" s="77" t="n">
+        <x:f>F6-C6</x:f>
+        <x:v>0.025096192787544935</x:v>
+      </x:c>
+      <x:c r="H6" s="77" t="n">
+        <x:v>0.6741975664405727</x:v>
+      </x:c>
+      <x:c r="I6" s="77" t="n">
+        <x:f>H6-C6</x:f>
+        <x:v>0.018999238924250705</x:v>
+      </x:c>
+      <x:c r="J6" s="77" t="n">
+        <x:v>0.6447678662943364</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="76" t="str">
+        <x:v>p03</x:v>
+      </x:c>
+      <x:c r="B7" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="77" t="n">
+        <x:v>0.0995287356545802</x:v>
+      </x:c>
+      <x:c r="D7" s="77" t="n">
+        <x:v>0.17441678491295232</x:v>
+      </x:c>
+      <x:c r="E7" s="77" t="n">
+        <x:f>D7-C7</x:f>
+        <x:v>0.07488804925837211</x:v>
+      </x:c>
+      <x:c r="F7" s="77" t="n">
+        <x:v>0.2067137020942127</x:v>
+      </x:c>
+      <x:c r="G7" s="77" t="n">
+        <x:f>F7-C7</x:f>
+        <x:v>0.10718496643963249</x:v>
+      </x:c>
+      <x:c r="H7" s="77" t="n">
+        <x:v>0.16930032683497043</x:v>
+      </x:c>
+      <x:c r="I7" s="77" t="n">
+        <x:f>H7-C7</x:f>
+        <x:v>0.06977159118039022</x:v>
+      </x:c>
+      <x:c r="J7" s="77" t="n">
+        <x:v>0.17441678491295232</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="76" t="str">
+        <x:v>p04</x:v>
+      </x:c>
+      <x:c r="B8" s="76" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C8" s="77" t="n">
+        <x:v>1.2006884882495612</x:v>
+      </x:c>
+      <x:c r="D8" s="77" t="n">
+        <x:v>1.2068380536505807</x:v>
+      </x:c>
+      <x:c r="E8" s="77" t="n">
+        <x:f>D8-C8</x:f>
+        <x:v>0.006149565401019519</x:v>
+      </x:c>
+      <x:c r="F8" s="77" t="n">
+        <x:v>1.1830417047568231</x:v>
+      </x:c>
+      <x:c r="G8" s="77" t="n">
+        <x:f>F8-C8</x:f>
+        <x:v>-0.017646783492738072</x:v>
+      </x:c>
+      <x:c r="H8" s="77" t="n">
+        <x:v>1.2355777756943005</x:v>
+      </x:c>
+      <x:c r="I8" s="77" t="n">
+        <x:f>H8-C8</x:f>
+        <x:v>0.03488928744473929</x:v>
+      </x:c>
+      <x:c r="J8" s="77" t="n">
+        <x:v>1.2068380536505807</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="76" t="str">
+        <x:v>p05</x:v>
+      </x:c>
+      <x:c r="B9" s="76" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C9" s="77" t="n">
+        <x:v>1.6695828759409508</x:v>
+      </x:c>
+      <x:c r="D9" s="77" t="n">
+        <x:v>2.1473031919305465</x:v>
+      </x:c>
+      <x:c r="E9" s="77" t="n">
+        <x:f>D9-C9</x:f>
+        <x:v>0.47772031598959575</x:v>
+      </x:c>
+      <x:c r="F9" s="77" t="n">
+        <x:v>1.7442419771178912</x:v>
+      </x:c>
+      <x:c r="G9" s="77" t="n">
+        <x:f>F9-C9</x:f>
+        <x:v>0.07465910117694041</x:v>
+      </x:c>
+      <x:c r="H9" s="77" t="n">
+        <x:v>1.7093542588665314</x:v>
+      </x:c>
+      <x:c r="I9" s="77" t="n">
+        <x:f>H9-C9</x:f>
+        <x:v>0.03977138292558058</x:v>
+      </x:c>
+      <x:c r="J9" s="77" t="n">
+        <x:v>2.1473031919305465</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="76" t="str">
+        <x:v>p06</x:v>
+      </x:c>
+      <x:c r="B10" s="76" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C10" s="77" t="n">
+        <x:v>1.3459179912832273</x:v>
+      </x:c>
+      <x:c r="D10" s="77" t="n">
+        <x:v>1.1412870674482067</x:v>
+      </x:c>
+      <x:c r="E10" s="77" t="n">
+        <x:f>D10-C10</x:f>
+        <x:v>-0.20463092383502057</x:v>
+      </x:c>
+      <x:c r="F10" s="77" t="n">
+        <x:v>1.1175196348823742</x:v>
+      </x:c>
+      <x:c r="G10" s="77" t="n">
+        <x:f>F10-C10</x:f>
+        <x:v>-0.22839835640085315</x:v>
+      </x:c>
+      <x:c r="H10" s="77" t="n">
+        <x:v>1.1748173775503725</x:v>
+      </x:c>
+      <x:c r="I10" s="77" t="n">
+        <x:f>H10-C10</x:f>
+        <x:v>-0.1711006137328548</x:v>
+      </x:c>
+      <x:c r="J10" s="77" t="n">
+        <x:v>1.1412870674482067</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="76" t="str">
+        <x:v>p07</x:v>
+      </x:c>
+      <x:c r="B11" s="76" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C11" s="77" t="n">
+        <x:v>1.7726823590623266</x:v>
+      </x:c>
+      <x:c r="D11" s="77" t="n">
+        <x:v>1.3551139161088712</x:v>
+      </x:c>
+      <x:c r="E11" s="77" t="n">
+        <x:f>D11-C11</x:f>
+        <x:v>-0.4175684429534554</x:v>
+      </x:c>
+      <x:c r="F11" s="77" t="n">
+        <x:v>1.3636408849210948</x:v>
+      </x:c>
+      <x:c r="G11" s="77" t="n">
+        <x:f>F11-C11</x:f>
+        <x:v>-0.4090414741412318</x:v>
+      </x:c>
+      <x:c r="H11" s="77" t="n">
+        <x:v>1.497051066688677</x:v>
+      </x:c>
+      <x:c r="I11" s="77" t="n">
+        <x:f>H11-C11</x:f>
+        <x:v>-0.2756312923736497</x:v>
+      </x:c>
+      <x:c r="J11" s="77" t="n">
+        <x:v>1.3551139161088712</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="76" t="str">
+        <x:v>p08</x:v>
+      </x:c>
+      <x:c r="B12" s="76" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C12" s="77" t="n">
+        <x:v>1.6467649477612443</x:v>
+      </x:c>
+      <x:c r="D12" s="77" t="n">
+        <x:v>1.331140876563422</x:v>
+      </x:c>
+      <x:c r="E12" s="77" t="n">
+        <x:f>D12-C12</x:f>
+        <x:v>-0.3156240711978222</x:v>
+      </x:c>
+      <x:c r="F12" s="77" t="n">
+        <x:v>1.361340228412525</x:v>
+      </x:c>
+      <x:c r="G12" s="77" t="n">
+        <x:f>F12-C12</x:f>
+        <x:v>-0.28542471934871916</x:v>
+      </x:c>
+      <x:c r="H12" s="77" t="n">
+        <x:v>1.465424185764665</x:v>
+      </x:c>
+      <x:c r="I12" s="77" t="n">
+        <x:f>H12-C12</x:f>
+        <x:v>-0.18134076199657923</x:v>
+      </x:c>
+      <x:c r="J12" s="77" t="n">
+        <x:v>1.331140876563422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="76" t="str">
+        <x:v>p09</x:v>
+      </x:c>
+      <x:c r="B13" s="76" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C13" s="77" t="n">
+        <x:v>1.438914622426954</x:v>
+      </x:c>
+      <x:c r="D13" s="77" t="n">
+        <x:v>1.2271874632143245</x:v>
+      </x:c>
+      <x:c r="E13" s="77" t="n">
+        <x:f>D13-C13</x:f>
+        <x:v>-0.21172715921262952</x:v>
+      </x:c>
+      <x:c r="F13" s="77" t="n">
+        <x:v>1.2916569077966522</x:v>
+      </x:c>
+      <x:c r="G13" s="77" t="n">
+        <x:f>F13-C13</x:f>
+        <x:v>-0.1472577146303018</x:v>
+      </x:c>
+      <x:c r="H13" s="77" t="n">
+        <x:v>1.2454164814693112</x:v>
+      </x:c>
+      <x:c r="I13" s="77" t="n">
+        <x:f>H13-C13</x:f>
+        <x:v>-0.19349814095764284</x:v>
+      </x:c>
+      <x:c r="J13" s="77" t="n">
+        <x:v>1.4199796097549302</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="76" t="str">
+        <x:v>p10</x:v>
+      </x:c>
+      <x:c r="B14" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="77" t="n">
+        <x:v>3.2832124090462127</x:v>
+      </x:c>
+      <x:c r="D14" s="77" t="n">
+        <x:v>3.2762154161719366</x:v>
+      </x:c>
+      <x:c r="E14" s="77" t="n">
+        <x:f>D14-C14</x:f>
+        <x:v>-0.006996992874276131</x:v>
+      </x:c>
+      <x:c r="F14" s="77" t="n">
+        <x:v>3.356959243036494</x:v>
+      </x:c>
+      <x:c r="G14" s="77" t="n">
+        <x:f>F14-C14</x:f>
+        <x:v>0.07374683399028115</x:v>
+      </x:c>
+      <x:c r="H14" s="77" t="n">
+        <x:v>3.3493002558641862</x:v>
+      </x:c>
+      <x:c r="I14" s="77" t="n">
+        <x:f>H14-C14</x:f>
+        <x:v>0.06608784681797353</x:v>
+      </x:c>
+      <x:c r="J14" s="77" t="n">
+        <x:v>3.2762154161719366</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="76" t="str">
+        <x:v>p11</x:v>
+      </x:c>
+      <x:c r="B15" s="76" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C15" s="77" t="n">
+        <x:v>1.9373546513548079</x:v>
+      </x:c>
+      <x:c r="D15" s="77" t="n">
+        <x:v>1.72371580693681</x:v>
+      </x:c>
+      <x:c r="E15" s="77" t="n">
+        <x:f>D15-C15</x:f>
+        <x:v>-0.21363884441799796</x:v>
+      </x:c>
+      <x:c r="F15" s="77" t="n">
+        <x:v>1.7044267994994975</x:v>
+      </x:c>
+      <x:c r="G15" s="77" t="n">
+        <x:f>F15-C15</x:f>
+        <x:v>-0.2329278518553104</x:v>
+      </x:c>
+      <x:c r="H15" s="77" t="n">
+        <x:v>1.7749116904960978</x:v>
+      </x:c>
+      <x:c r="I15" s="77" t="n">
+        <x:f>H15-C15</x:f>
+        <x:v>-0.16244296085871013</x:v>
+      </x:c>
+      <x:c r="J15" s="77" t="n">
+        <x:v>1.72371580693681</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="76" t="str">
+        <x:v>p12</x:v>
+      </x:c>
+      <x:c r="B16" s="76" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C16" s="77" t="n">
+        <x:v>0.3805812828660011</x:v>
+      </x:c>
+      <x:c r="D16" s="77" t="n">
+        <x:v>0.2714568794802408</x:v>
+      </x:c>
+      <x:c r="E16" s="77" t="n">
+        <x:f>D16-C16</x:f>
+        <x:v>-0.10912440338576035</x:v>
+      </x:c>
+      <x:c r="F16" s="77" t="n">
+        <x:v>0.2820074357868543</x:v>
+      </x:c>
+      <x:c r="G16" s="77" t="n">
+        <x:f>F16-C16</x:f>
+        <x:v>-0.09857384707914685</x:v>
+      </x:c>
+      <x:c r="H16" s="77" t="n">
+        <x:v>0.1730025095471892</x:v>
+      </x:c>
+      <x:c r="I16" s="77" t="n">
+        <x:f>H16-C16</x:f>
+        <x:v>-0.20757877331881192</x:v>
+      </x:c>
+      <x:c r="J16" s="77" t="n">
+        <x:v>0.2714568794802408</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="76" t="str">
+        <x:v>p13</x:v>
+      </x:c>
+      <x:c r="B17" s="76" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C17" s="77" t="n">
+        <x:v>0.7990183786925269</x:v>
+      </x:c>
+      <x:c r="D17" s="77" t="n">
+        <x:v>0.9587573389944235</x:v>
+      </x:c>
+      <x:c r="E17" s="77" t="n">
+        <x:f>D17-C17</x:f>
+        <x:v>0.1597389603018966</x:v>
+      </x:c>
+      <x:c r="F17" s="77" t="n">
+        <x:v>0.9667511075508379</x:v>
+      </x:c>
+      <x:c r="G17" s="77" t="n">
+        <x:f>F17-C17</x:f>
+        <x:v>0.16773272885831103</x:v>
+      </x:c>
+      <x:c r="H17" s="77" t="n">
+        <x:v>0.8592712610970663</x:v>
+      </x:c>
+      <x:c r="I17" s="77" t="n">
+        <x:f>H17-C17</x:f>
+        <x:v>0.06025288240453941</x:v>
+      </x:c>
+      <x:c r="J17" s="77" t="n">
+        <x:v>0.9587573389944235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="76" t="str">
+        <x:v>p14</x:v>
+      </x:c>
+      <x:c r="B18" s="76" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C18" s="77" t="n">
+        <x:v>0.7577866369295649</x:v>
+      </x:c>
+      <x:c r="D18" s="77" t="n">
+        <x:v>0.653035042472271</x:v>
+      </x:c>
+      <x:c r="E18" s="77" t="n">
+        <x:f>D18-C18</x:f>
+        <x:v>-0.10475159445729398</x:v>
+      </x:c>
+      <x:c r="F18" s="77" t="n">
+        <x:v>0.6909513561227043</x:v>
+      </x:c>
+      <x:c r="G18" s="77" t="n">
+        <x:f>F18-C18</x:f>
+        <x:v>-0.06683528080686063</x:v>
+      </x:c>
+      <x:c r="H18" s="77" t="n">
+        <x:v>0.6517975489339697</x:v>
+      </x:c>
+      <x:c r="I18" s="77" t="n">
+        <x:f>H18-C18</x:f>
+        <x:v>-0.10598908799559525</x:v>
+      </x:c>
+      <x:c r="J18" s="77" t="n">
+        <x:v>0.653035042472271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="76" t="str">
+        <x:v>p15</x:v>
+      </x:c>
+      <x:c r="B19" s="76" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C19" s="77" t="n">
+        <x:v>1.9214974186959535</x:v>
+      </x:c>
+      <x:c r="D19" s="77" t="n">
+        <x:v>1.8126158883083692</x:v>
+      </x:c>
+      <x:c r="E19" s="77" t="n">
+        <x:f>D19-C19</x:f>
+        <x:v>-0.1088815303875843</x:v>
+      </x:c>
+      <x:c r="F19" s="77" t="n">
+        <x:v>1.9044758992743513</x:v>
+      </x:c>
+      <x:c r="G19" s="77" t="n">
+        <x:f>F19-C19</x:f>
+        <x:v>-0.017021519421602127</x:v>
+      </x:c>
+      <x:c r="H19" s="77" t="n">
+        <x:v>1.8744105611659267</x:v>
+      </x:c>
+      <x:c r="I19" s="77" t="n">
+        <x:f>H19-C19</x:f>
+        <x:v>-0.04708685753002673</x:v>
+      </x:c>
+      <x:c r="J19" s="77" t="n">
+        <x:v>1.8126158883083692</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="34" customHeight="1">
+      <x:c r="A21" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_participant_losses.csv</x:v>
+      </x:c>
+      <x:c r="B21" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_participant_losses.csv</x:v>
+      </x:c>
+      <x:c r="C21" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_participant_losses.csv</x:v>
+      </x:c>
+      <x:c r="D21" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_participant_losses.csv</x:v>
+      </x:c>
+      <x:c r="E21" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_participant_losses.csv</x:v>
+      </x:c>
+      <x:c r="F21" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_participant_losses.csv</x:v>
+      </x:c>
+      <x:c r="G21" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_participant_losses.csv</x:v>
+      </x:c>
+      <x:c r="H21" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_participant_losses.csv</x:v>
+      </x:c>
+      <x:c r="I21" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_participant_losses.csv</x:v>
+      </x:c>
+      <x:c r="J21" s="81" t="str">
+        <x:v>Source file: analysis/reviewer_round5_participant_losses.csv</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+    <x:mergeCell ref="A21:J21"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="58" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="67" t="str">
+        <x:v>PMData sample-flow reconciliation</x:v>
+      </x:c>
+      <x:c r="B1" s="67" t="str">
+        <x:v>PMData sample-flow reconciliation</x:v>
+      </x:c>
+      <x:c r="C1" s="67" t="str">
+        <x:v>PMData sample-flow reconciliation</x:v>
+      </x:c>
+      <x:c r="D1" s="67" t="str">
+        <x:v>PMData sample-flow reconciliation</x:v>
+      </x:c>
+      <x:c r="E1" s="67" t="str">
+        <x:v>PMData sample-flow reconciliation</x:v>
+      </x:c>
+      <x:c r="F1" s="67" t="str">
+        <x:v>PMData sample-flow reconciliation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="70" t="str">
+        <x:v>Sequential construction and rule-specific reconstructions are separated because rematching can admit newly eligible pairs.</x:v>
+      </x:c>
+      <x:c r="B2" s="70" t="str">
+        <x:v>Sequential construction and rule-specific reconstructions are separated because rematching can admit newly eligible pairs.</x:v>
+      </x:c>
+      <x:c r="C2" s="70" t="str">
+        <x:v>Sequential construction and rule-specific reconstructions are separated because rematching can admit newly eligible pairs.</x:v>
+      </x:c>
+      <x:c r="D2" s="70" t="str">
+        <x:v>Sequential construction and rule-specific reconstructions are separated because rematching can admit newly eligible pairs.</x:v>
+      </x:c>
+      <x:c r="E2" s="70" t="str">
+        <x:v>Sequential construction and rule-specific reconstructions are separated because rematching can admit newly eligible pairs.</x:v>
+      </x:c>
+      <x:c r="F2" s="70" t="str">
+        <x:v>Sequential construction and rule-specific reconstructions are separated because rematching can admit newly eligible pairs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="75" t="str">
+        <x:v>stage</x:v>
+      </x:c>
+      <x:c r="B4" s="75" t="str">
+        <x:v>sessions</x:v>
+      </x:c>
+      <x:c r="C4" s="75" t="str">
+        <x:v>definition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="76" t="str">
+        <x:v>Archived PMSys RPE records</x:v>
+      </x:c>
+      <x:c r="B5" s="76" t="n">
+        <x:v>783</x:v>
+      </x:c>
+      <x:c r="C5" s="76" t="str">
+        <x:v>all archived RPE rows</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="76" t="str">
+        <x:v>Broad tracker-linked pairs</x:v>
+      </x:c>
+      <x:c r="B6" s="76" t="n">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="C6" s="76" t="str">
+        <x:v>timestamp and activity-compatible links</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="76" t="str">
+        <x:v>Bidirectionally unique broad pairs</x:v>
+      </x:c>
+      <x:c r="B7" s="76" t="n">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="C7" s="76" t="str">
+        <x:v>unique in both matching directions</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="76" t="str">
+        <x:v>Unique broad pairs passing HR quality control</x:v>
+      </x:c>
+      <x:c r="B8" s="76" t="n">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="C8" s="76" t="str">
+        <x:v>heart-rate signal criteria satisfied</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="76" t="str">
+        <x:v>Primary analysis sessions</x:v>
+      </x:c>
+      <x:c r="B9" s="76" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C9" s="76" t="str">
+        <x:v>all primary matching and outcome criteria satisfied</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="82" t="str">
+        <x:v>Rule-specific matching sensitivity</x:v>
+      </x:c>
+      <x:c r="B12" s="82"/>
+      <x:c r="C12" s="82"/>
+      <x:c r="D12" s="82"/>
+      <x:c r="E12" s="82"/>
+      <x:c r="F12" s="82"/>
+    </x:row>
+    <x:row r="13" ht="32" customHeight="1">
+      <x:c r="A13" s="75" t="str">
+        <x:v>rule</x:v>
+      </x:c>
+      <x:c r="B13" s="75" t="str">
+        <x:v>selected_pairs</x:v>
+      </x:c>
+      <x:c r="C13" s="75" t="str">
+        <x:v>bidirectionally_unique_pairs</x:v>
+      </x:c>
+      <x:c r="D13" s="75" t="str">
+        <x:v>original_primary_pairs_retained</x:v>
+      </x:c>
+      <x:c r="E13" s="75" t="str">
+        <x:v>rebuilt_analysis_sessions</x:v>
+      </x:c>
+      <x:c r="F13" s="75" t="str">
+        <x:v>interpretation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="76" t="str">
+        <x:v>Primary 15-180 min</x:v>
+      </x:c>
+      <x:c r="B14" s="76" t="n">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="C14" s="76" t="n">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="D14" s="76" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="E14" s="76" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="F14" s="76" t="str">
+        <x:v>Retained counts track IDs from the 255-session primary set; rebuilt counts include newly eligible matches after the rule-specific reconstruction and full quality control.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="76" t="str">
+        <x:v>15-90 min</x:v>
+      </x:c>
+      <x:c r="B15" s="76" t="n">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="C15" s="76" t="n">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="D15" s="76" t="n">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="E15" s="76" t="n">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="F15" s="76" t="str">
+        <x:v>Retained counts track IDs from the 255-session primary set; rebuilt counts include newly eligible matches after the rule-specific reconstruction and full quality control.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="76" t="str">
+        <x:v>30-120 min</x:v>
+      </x:c>
+      <x:c r="B16" s="76" t="n">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="C16" s="76" t="n">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="D16" s="76" t="n">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="E16" s="76" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F16" s="76" t="str">
+        <x:v>Retained counts track IDs from the 255-session primary set; rebuilt counts include newly eligible matches after the rule-specific reconstruction and full quality control.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="76" t="str">
+        <x:v>Duration difference &lt;=10 min</x:v>
+      </x:c>
+      <x:c r="B17" s="76" t="n">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="C17" s="76" t="n">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="D17" s="76" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="E17" s="76" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F17" s="76" t="str">
+        <x:v>Retained counts track IDs from the 255-session primary set; rebuilt counts include newly eligible matches after the rule-specific reconstruction and full quality control.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="76" t="str">
+        <x:v>Delay-priority cost</x:v>
+      </x:c>
+      <x:c r="B18" s="76" t="n">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="C18" s="76" t="n">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="D18" s="76" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="E18" s="76" t="n">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="F18" s="76" t="str">
+        <x:v>Retained counts track IDs from the 255-session primary set; rebuilt counts include newly eligible matches after the rule-specific reconstruction and full quality control.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="76" t="str">
+        <x:v>Duration-priority cost</x:v>
+      </x:c>
+      <x:c r="B19" s="76" t="n">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="C19" s="76" t="n">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="D19" s="76" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="E19" s="76" t="n">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="F19" s="76" t="str">
+        <x:v>Retained counts track IDs from the 255-session primary set; rebuilt counts include newly eligible matches after the rule-specific reconstruction and full quality control.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="34" customHeight="1">
+      <x:c r="A21" s="81" t="str">
+        <x:v>Source files: analysis/reviewer_round5_primary_sample_flow.csv and analysis/reviewer_round5_sensitivity_sample_flow.csv</x:v>
+      </x:c>
+      <x:c r="B21" s="81" t="str">
+        <x:v>Source files: analysis/reviewer_round5_primary_sample_flow.csv and analysis/reviewer_round5_sensitivity_sample_flow.csv</x:v>
+      </x:c>
+      <x:c r="C21" s="81" t="str">
+        <x:v>Source files: analysis/reviewer_round5_primary_sample_flow.csv and analysis/reviewer_round5_sensitivity_sample_flow.csv</x:v>
+      </x:c>
+      <x:c r="D21" s="81" t="str">
+        <x:v>Source files: analysis/reviewer_round5_primary_sample_flow.csv and analysis/reviewer_round5_sensitivity_sample_flow.csv</x:v>
+      </x:c>
+      <x:c r="E21" s="81" t="str">
+        <x:v>Source files: analysis/reviewer_round5_primary_sample_flow.csv and analysis/reviewer_round5_sensitivity_sample_flow.csv</x:v>
+      </x:c>
+      <x:c r="F21" s="81" t="str">
+        <x:v>Source files: analysis/reviewer_round5_primary_sample_flow.csv and analysis/reviewer_round5_sensitivity_sample_flow.csv</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A12:F12"/>
+    <x:mergeCell ref="A21:F21"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="17" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="17" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="17" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="17" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="17" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="17" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="17" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="17" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="17" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="17" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="B1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="C1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="D1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="E1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="F1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="G1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="H1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="I1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="J1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="K1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="L1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="M1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="N1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="O1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="P1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="Q1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="R1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="S1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="T1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+      <x:c r="U1" s="67" t="str">
+        <x:v>WEEE repeated-measures agreement</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="B2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="C2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="D2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="E2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="F2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="G2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="H2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="I2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="J2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="K2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="L2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="M2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="N2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="O2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="P2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="Q2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="R2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="S2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="T2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+      <x:c r="U2" s="70" t="str">
+        <x:v>Primary manuscript inference uses Zephyr (16 participants, 77 stages). Apple Watch and E4 rows are retained only to disclose inadequate participant coverage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="75" t="str">
+        <x:v>Device</x:v>
+      </x:c>
+      <x:c r="B4" s="75" t="str">
+        <x:v>Index</x:v>
+      </x:c>
+      <x:c r="C4" s="75" t="str">
+        <x:v>Participants</x:v>
+      </x:c>
+      <x:c r="D4" s="75" t="str">
+        <x:v>Stages</x:v>
+      </x:c>
+      <x:c r="E4" s="75" t="str">
+        <x:v>Balanced bias</x:v>
+      </x:c>
+      <x:c r="F4" s="75" t="str">
+        <x:v>Between-person difference variance</x:v>
+      </x:c>
+      <x:c r="G4" s="75" t="str">
+        <x:v>Within-person difference variance</x:v>
+      </x:c>
+      <x:c r="H4" s="75" t="str">
+        <x:v>RM LoA lower</x:v>
+      </x:c>
+      <x:c r="I4" s="75" t="str">
+        <x:v>RM LoA upper</x:v>
+      </x:c>
+      <x:c r="J4" s="75" t="str">
+        <x:v>Balanced CCC</x:v>
+      </x:c>
+      <x:c r="K4" s="75" t="str">
+        <x:v>Participant-centered r</x:v>
+      </x:c>
+      <x:c r="L4" s="75" t="str">
+        <x:v>Bias CI lower</x:v>
+      </x:c>
+      <x:c r="M4" s="75" t="str">
+        <x:v>Bias CI upper</x:v>
+      </x:c>
+      <x:c r="N4" s="75" t="str">
+        <x:v>LoA lower CI lower</x:v>
+      </x:c>
+      <x:c r="O4" s="75" t="str">
+        <x:v>LoA lower CI upper</x:v>
+      </x:c>
+      <x:c r="P4" s="75" t="str">
+        <x:v>LoA upper CI lower</x:v>
+      </x:c>
+      <x:c r="Q4" s="75" t="str">
+        <x:v>LoA upper CI upper</x:v>
+      </x:c>
+      <x:c r="R4" s="75" t="str">
+        <x:v>CCC CI lower</x:v>
+      </x:c>
+      <x:c r="S4" s="75" t="str">
+        <x:v>CCC CI upper</x:v>
+      </x:c>
+      <x:c r="T4" s="75" t="str">
+        <x:v>Centered r CI lower</x:v>
+      </x:c>
+      <x:c r="U4" s="75" t="str">
+        <x:v>Centered r CI upper</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="76" t="str">
+        <x:v>apple_watch</x:v>
+      </x:c>
+      <x:c r="B5" s="76" t="str">
+        <x:v>mean_hrr</x:v>
+      </x:c>
+      <x:c r="C5" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="76" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E5" s="77" t="n">
+        <x:v>-0.42749684422358447</x:v>
+      </x:c>
+      <x:c r="F5" s="77"/>
+      <x:c r="G5" s="77" t="n">
+        <x:v>0.00701739666078539</x:v>
+      </x:c>
+      <x:c r="H5" s="77"/>
+      <x:c r="I5" s="77"/>
+      <x:c r="J5" s="77" t="n">
+        <x:v>0.004394910473526646</x:v>
+      </x:c>
+      <x:c r="K5" s="77" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L5" s="77" t="n">
+        <x:v>-0.42749684422358447</x:v>
+      </x:c>
+      <x:c r="M5" s="77" t="n">
+        <x:v>-0.42749684422358447</x:v>
+      </x:c>
+      <x:c r="N5" s="77"/>
+      <x:c r="O5" s="77"/>
+      <x:c r="P5" s="77"/>
+      <x:c r="Q5" s="77"/>
+      <x:c r="R5" s="77" t="n">
+        <x:v>0.004394910473526646</x:v>
+      </x:c>
+      <x:c r="S5" s="77" t="n">
+        <x:v>0.004394910473526646</x:v>
+      </x:c>
+      <x:c r="T5" s="77" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U5" s="77" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="76" t="str">
+        <x:v>apple_watch</x:v>
+      </x:c>
+      <x:c r="B6" s="76" t="str">
+        <x:v>thrr_i</x:v>
+      </x:c>
+      <x:c r="C6" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D6" s="76" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E6" s="77" t="n">
+        <x:v>-0.4120317476714055</x:v>
+      </x:c>
+      <x:c r="F6" s="77"/>
+      <x:c r="G6" s="77" t="n">
+        <x:v>0.009276650435766006</x:v>
+      </x:c>
+      <x:c r="H6" s="77"/>
+      <x:c r="I6" s="77"/>
+      <x:c r="J6" s="77" t="n">
+        <x:v>0.006287974137288232</x:v>
+      </x:c>
+      <x:c r="K6" s="77" t="n">
+        <x:v>1.0000000000000002</x:v>
+      </x:c>
+      <x:c r="L6" s="77" t="n">
+        <x:v>-0.4120317476714055</x:v>
+      </x:c>
+      <x:c r="M6" s="77" t="n">
+        <x:v>-0.4120317476714055</x:v>
+      </x:c>
+      <x:c r="N6" s="77"/>
+      <x:c r="O6" s="77"/>
+      <x:c r="P6" s="77"/>
+      <x:c r="Q6" s="77"/>
+      <x:c r="R6" s="77" t="n">
+        <x:v>0.006287974137288232</x:v>
+      </x:c>
+      <x:c r="S6" s="77" t="n">
+        <x:v>0.006287974137288232</x:v>
+      </x:c>
+      <x:c r="T6" s="77" t="n">
+        <x:v>1.0000000000000002</x:v>
+      </x:c>
+      <x:c r="U6" s="77" t="n">
+        <x:v>1.0000000000000002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="76" t="str">
+        <x:v>apple_watch</x:v>
+      </x:c>
+      <x:c r="B7" s="76" t="str">
+        <x:v>delta_tilt</x:v>
+      </x:c>
+      <x:c r="C7" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" s="76" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E7" s="77" t="n">
+        <x:v>0.01546509655217905</x:v>
+      </x:c>
+      <x:c r="F7" s="77"/>
+      <x:c r="G7" s="77" t="n">
+        <x:v>0.00015738873229050808</x:v>
+      </x:c>
+      <x:c r="H7" s="77"/>
+      <x:c r="I7" s="77"/>
+      <x:c r="J7" s="77" t="n">
+        <x:v>0.06095116141173844</x:v>
+      </x:c>
+      <x:c r="K7" s="77" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L7" s="77" t="n">
+        <x:v>0.01546509655217905</x:v>
+      </x:c>
+      <x:c r="M7" s="77" t="n">
+        <x:v>0.01546509655217905</x:v>
+      </x:c>
+      <x:c r="N7" s="77"/>
+      <x:c r="O7" s="77"/>
+      <x:c r="P7" s="77"/>
+      <x:c r="Q7" s="77"/>
+      <x:c r="R7" s="77" t="n">
+        <x:v>0.06095116141173844</x:v>
+      </x:c>
+      <x:c r="S7" s="77" t="n">
+        <x:v>0.06095116141173844</x:v>
+      </x:c>
+      <x:c r="T7" s="77" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U7" s="77" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="76" t="str">
+        <x:v>e4</x:v>
+      </x:c>
+      <x:c r="B8" s="76" t="str">
+        <x:v>mean_hrr</x:v>
+      </x:c>
+      <x:c r="C8" s="76" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D8" s="76" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E8" s="77" t="n">
+        <x:v>0.011972552195592234</x:v>
+      </x:c>
+      <x:c r="F8" s="77" t="n">
+        <x:v>0.07758612098469439</x:v>
+      </x:c>
+      <x:c r="G8" s="77" t="n">
+        <x:v>0.009621295097330819</x:v>
+      </x:c>
+      <x:c r="H8" s="77" t="n">
+        <x:v>-0.566833122984522</x:v>
+      </x:c>
+      <x:c r="I8" s="77" t="n">
+        <x:v>0.5907782273757065</x:v>
+      </x:c>
+      <x:c r="J8" s="77" t="n">
+        <x:v>-0.28400163814416163</x:v>
+      </x:c>
+      <x:c r="K8" s="77" t="n">
+        <x:v>0.7242072426030246</x:v>
+      </x:c>
+      <x:c r="L8" s="77" t="n">
+        <x:v>-0.19100129899386492</x:v>
+      </x:c>
+      <x:c r="M8" s="77" t="n">
+        <x:v>0.2149464033850494</x:v>
+      </x:c>
+      <x:c r="N8" s="77" t="n">
+        <x:v>-0.566833122984522</x:v>
+      </x:c>
+      <x:c r="O8" s="77" t="n">
+        <x:v>-0.006063381541955376</x:v>
+      </x:c>
+      <x:c r="P8" s="77" t="n">
+        <x:v>-0.03264407794496155</x:v>
+      </x:c>
+      <x:c r="Q8" s="77" t="n">
+        <x:v>0.5907782273757065</x:v>
+      </x:c>
+      <x:c r="R8" s="77" t="n">
+        <x:v>-0.28400163814416163</x:v>
+      </x:c>
+      <x:c r="S8" s="77" t="n">
+        <x:v>0.026880214821956898</x:v>
+      </x:c>
+      <x:c r="T8" s="77" t="n">
+        <x:v>0.7242072426030246</x:v>
+      </x:c>
+      <x:c r="U8" s="77" t="n">
+        <x:v>1.0000000000000002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="76" t="str">
+        <x:v>e4</x:v>
+      </x:c>
+      <x:c r="B9" s="76" t="str">
+        <x:v>thrr_i</x:v>
+      </x:c>
+      <x:c r="C9" s="76" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D9" s="76" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E9" s="77" t="n">
+        <x:v>0.29759352624063135</x:v>
+      </x:c>
+      <x:c r="F9" s="77" t="n">
+        <x:v>0.2966176427432425</x:v>
+      </x:c>
+      <x:c r="G9" s="77" t="n">
+        <x:v>0.016262330770474</x:v>
+      </x:c>
+      <x:c r="H9" s="77" t="n">
+        <x:v>-0.7987457033093712</x:v>
+      </x:c>
+      <x:c r="I9" s="77" t="n">
+        <x:v>1.3939327557906338</x:v>
+      </x:c>
+      <x:c r="J9" s="77" t="n">
+        <x:v>-0.44398257057384943</x:v>
+      </x:c>
+      <x:c r="K9" s="77" t="n">
+        <x:v>-0.855734879751444</x:v>
+      </x:c>
+      <x:c r="L9" s="77" t="n">
+        <x:v>-0.09275811531380065</x:v>
+      </x:c>
+      <x:c r="M9" s="77" t="n">
+        <x:v>0.6879451677950633</x:v>
+      </x:c>
+      <x:c r="N9" s="77" t="n">
+        <x:v>-0.7987457033093712</x:v>
+      </x:c>
+      <x:c r="O9" s="77" t="n">
+        <x:v>0.47742423168987336</x:v>
+      </x:c>
+      <x:c r="P9" s="77" t="n">
+        <x:v>0.19119201276699513</x:v>
+      </x:c>
+      <x:c r="Q9" s="77" t="n">
+        <x:v>1.3939327557906338</x:v>
+      </x:c>
+      <x:c r="R9" s="77" t="n">
+        <x:v>-0.4439825705738496</x:v>
+      </x:c>
+      <x:c r="S9" s="77" t="n">
+        <x:v>-0.0016629031813126896</x:v>
+      </x:c>
+      <x:c r="T9" s="77" t="n">
+        <x:v>-1.0000000000000002</x:v>
+      </x:c>
+      <x:c r="U9" s="77" t="n">
+        <x:v>-0.855734879751444</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="76" t="str">
+        <x:v>e4</x:v>
+      </x:c>
+      <x:c r="B10" s="76" t="str">
+        <x:v>delta_tilt</x:v>
+      </x:c>
+      <x:c r="C10" s="76" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D10" s="76" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E10" s="77" t="n">
+        <x:v>0.28562097404503906</x:v>
+      </x:c>
+      <x:c r="F10" s="77" t="n">
+        <x:v>0.0691872151676574</x:v>
+      </x:c>
+      <x:c r="G10" s="77" t="n">
+        <x:v>0.0020673149529269606</x:v>
+      </x:c>
+      <x:c r="H10" s="77" t="n">
+        <x:v>-0.23757249199905905</x:v>
+      </x:c>
+      <x:c r="I10" s="77" t="n">
+        <x:v>0.8088144400891372</x:v>
+      </x:c>
+      <x:c r="J10" s="77" t="n">
+        <x:v>0.023929760286168326</x:v>
+      </x:c>
+      <x:c r="K10" s="77" t="n">
+        <x:v>-0.5372571806320987</x:v>
+      </x:c>
+      <x:c r="L10" s="77" t="n">
+        <x:v>0.0982431836800643</x:v>
+      </x:c>
+      <x:c r="M10" s="77" t="n">
+        <x:v>0.47299876441001387</x:v>
+      </x:c>
+      <x:c r="N10" s="77" t="n">
+        <x:v>-0.23757249199905905</x:v>
+      </x:c>
+      <x:c r="O10" s="77" t="n">
+        <x:v>0.462509915588199</x:v>
+      </x:c>
+      <x:c r="P10" s="77" t="n">
+        <x:v>0.22383609071195656</x:v>
+      </x:c>
+      <x:c r="Q10" s="77" t="n">
+        <x:v>0.8088144400891372</x:v>
+      </x:c>
+      <x:c r="R10" s="77" t="n">
+        <x:v>-0.06377508034879854</x:v>
+      </x:c>
+      <x:c r="S10" s="77" t="n">
+        <x:v>0.023929760286168326</x:v>
+      </x:c>
+      <x:c r="T10" s="77" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="U10" s="77" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="76" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="B11" s="76" t="str">
+        <x:v>mean_hrr</x:v>
+      </x:c>
+      <x:c r="C11" s="76" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D11" s="76" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E11" s="77" t="n">
+        <x:v>-0.024858046793567373</x:v>
+      </x:c>
+      <x:c r="F11" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="77" t="n">
+        <x:v>0.006391080674646548</x:v>
+      </x:c>
+      <x:c r="H11" s="77" t="n">
+        <x:v>-0.18154874696343126</x:v>
+      </x:c>
+      <x:c r="I11" s="77" t="n">
+        <x:v>0.13183265337629652</x:v>
+      </x:c>
+      <x:c r="J11" s="77" t="n">
+        <x:v>0.9168775264083271</x:v>
+      </x:c>
+      <x:c r="K11" s="77" t="n">
+        <x:v>0.9251380220583476</x:v>
+      </x:c>
+      <x:c r="L11" s="77" t="n">
+        <x:v>-0.036574906398400824</x:v>
+      </x:c>
+      <x:c r="M11" s="77" t="n">
+        <x:v>-0.009774815512390915</x:v>
+      </x:c>
+      <x:c r="N11" s="77" t="n">
+        <x:v>-0.24566620822728918</x:v>
+      </x:c>
+      <x:c r="O11" s="77" t="n">
+        <x:v>-0.10342762140728763</x:v>
+      </x:c>
+      <x:c r="P11" s="77" t="n">
+        <x:v>0.046756936136455214</x:v>
+      </x:c>
+      <x:c r="Q11" s="77" t="n">
+        <x:v>0.2170832678898023</x:v>
+      </x:c>
+      <x:c r="R11" s="77" t="n">
+        <x:v>0.7856849470521989</x:v>
+      </x:c>
+      <x:c r="S11" s="77" t="n">
+        <x:v>0.9740243291474556</x:v>
+      </x:c>
+      <x:c r="T11" s="77" t="n">
+        <x:v>0.7766037370296658</x:v>
+      </x:c>
+      <x:c r="U11" s="77" t="n">
+        <x:v>0.9908622143407204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="76" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="B12" s="76" t="str">
+        <x:v>thrr_i</x:v>
+      </x:c>
+      <x:c r="C12" s="76" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D12" s="76" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E12" s="77" t="n">
+        <x:v>-0.024566717840435154</x:v>
+      </x:c>
+      <x:c r="F12" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="77" t="n">
+        <x:v>0.014720217621991667</x:v>
+      </x:c>
+      <x:c r="H12" s="77" t="n">
+        <x:v>-0.2623674495816205</x:v>
+      </x:c>
+      <x:c r="I12" s="77" t="n">
+        <x:v>0.21323401390075017</x:v>
+      </x:c>
+      <x:c r="J12" s="77" t="n">
+        <x:v>0.8464359139148857</x:v>
+      </x:c>
+      <x:c r="K12" s="77" t="n">
+        <x:v>0.8464336809580291</x:v>
+      </x:c>
+      <x:c r="L12" s="77" t="n">
+        <x:v>-0.04391137019111345</x:v>
+      </x:c>
+      <x:c r="M12" s="77" t="n">
+        <x:v>-0.000738936223250524</x:v>
+      </x:c>
+      <x:c r="N12" s="77" t="n">
+        <x:v>-0.33901136050163794</x:v>
+      </x:c>
+      <x:c r="O12" s="77" t="n">
+        <x:v>-0.16119469532749045</x:v>
+      </x:c>
+      <x:c r="P12" s="77" t="n">
+        <x:v>0.08406097320493748</x:v>
+      </x:c>
+      <x:c r="Q12" s="77" t="n">
+        <x:v>0.32906587348297317</x:v>
+      </x:c>
+      <x:c r="R12" s="77" t="n">
+        <x:v>0.6541604454054335</x:v>
+      </x:c>
+      <x:c r="S12" s="77" t="n">
+        <x:v>0.9464125755630209</x:v>
+      </x:c>
+      <x:c r="T12" s="77" t="n">
+        <x:v>0.6495393524359105</x:v>
+      </x:c>
+      <x:c r="U12" s="77" t="n">
+        <x:v>0.9709472840972481</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="76" t="str">
+        <x:v>zephyr</x:v>
+      </x:c>
+      <x:c r="B13" s="76" t="str">
+        <x:v>delta_tilt</x:v>
+      </x:c>
+      <x:c r="C13" s="76" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D13" s="76" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E13" s="77" t="n">
+        <x:v>0.0002913289531322333</x:v>
+      </x:c>
+      <x:c r="F13" s="77" t="n">
+        <x:v>0.0001166982479605607</x:v>
+      </x:c>
+      <x:c r="G13" s="77" t="n">
+        <x:v>0.003207664959121301</x:v>
+      </x:c>
+      <x:c r="H13" s="77" t="n">
+        <x:v>-0.11271696143445693</x:v>
+      </x:c>
+      <x:c r="I13" s="77" t="n">
+        <x:v>0.1132996193407214</x:v>
+      </x:c>
+      <x:c r="J13" s="77" t="n">
+        <x:v>0.15640098297953384</x:v>
+      </x:c>
+      <x:c r="K13" s="77" t="n">
+        <x:v>0.17069049468212721</x:v>
+      </x:c>
+      <x:c r="L13" s="77" t="n">
+        <x:v>-0.01206018189894072</x:v>
+      </x:c>
+      <x:c r="M13" s="77" t="n">
+        <x:v>0.013920896408066477</x:v>
+      </x:c>
+      <x:c r="N13" s="77" t="n">
+        <x:v>-0.15184641188540243</x:v>
+      </x:c>
+      <x:c r="O13" s="77" t="n">
+        <x:v>-0.07248837209209001</x:v>
+      </x:c>
+      <x:c r="P13" s="77" t="n">
+        <x:v>0.0547118433665161</x:v>
+      </x:c>
+      <x:c r="Q13" s="77" t="n">
+        <x:v>0.1656540355948107</x:v>
+      </x:c>
+      <x:c r="R13" s="77" t="n">
+        <x:v>-0.006627259837690882</x:v>
+      </x:c>
+      <x:c r="S13" s="77" t="n">
+        <x:v>0.4669120906883816</x:v>
+      </x:c>
+      <x:c r="T13" s="77" t="n">
+        <x:v>-0.05321895299303002</x:v>
+      </x:c>
+      <x:c r="U13" s="77" t="n">
+        <x:v>0.5545165220140845</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="34" customHeight="1">
+      <x:c r="A15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="B15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="C15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="D15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="E15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="F15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="G15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="H15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="I15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="J15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="K15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="L15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="M15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="N15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="O15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="P15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="Q15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="R15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="S15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="T15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+      <x:c r="U15" s="81" t="str">
+        <x:v>Source file: external_validation/results/reviewer_round5_weee_repeated_agreement.csv | Public data: https://doi.org/10.5281/zenodo.6420886</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:U1"/>
+    <x:mergeCell ref="A2:U2"/>
+    <x:mergeCell ref="A15:U15"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="62" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="67" t="str">
+        <x:v>WEEE participant and stage attrition</x:v>
+      </x:c>
+      <x:c r="B1" s="67" t="str">
+        <x:v>WEEE participant and stage attrition</x:v>
+      </x:c>
+      <x:c r="C1" s="67" t="str">
+        <x:v>WEEE participant and stage attrition</x:v>
+      </x:c>
+      <x:c r="D1" s="67" t="str">
+        <x:v>WEEE participant and stage attrition</x:v>
+      </x:c>
+      <x:c r="E1" s="67" t="str">
+        <x:v>WEEE participant and stage attrition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="70" t="str">
+        <x:v>High-running-stage retention was 3/16 (18.8%); this intensity-dependent attrition limits upper-tail inference.</x:v>
+      </x:c>
+      <x:c r="B2" s="70" t="str">
+        <x:v>High-running-stage retention was 3/16 (18.8%); this intensity-dependent attrition limits upper-tail inference.</x:v>
+      </x:c>
+      <x:c r="C2" s="70" t="str">
+        <x:v>High-running-stage retention was 3/16 (18.8%); this intensity-dependent attrition limits upper-tail inference.</x:v>
+      </x:c>
+      <x:c r="D2" s="70" t="str">
+        <x:v>High-running-stage retention was 3/16 (18.8%); this intensity-dependent attrition limits upper-tail inference.</x:v>
+      </x:c>
+      <x:c r="E2" s="70" t="str">
+        <x:v>High-running-stage retention was 3/16 (18.8%); this intensity-dependent attrition limits upper-tail inference.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="75" t="str">
+        <x:v>stage</x:v>
+      </x:c>
+      <x:c r="B4" s="75" t="str">
+        <x:v>eligible_after_anchor_qc</x:v>
+      </x:c>
+      <x:c r="C4" s="75" t="str">
+        <x:v>included</x:v>
+      </x:c>
+      <x:c r="D4" s="75" t="str">
+        <x:v>excluded_stage_qc</x:v>
+      </x:c>
+      <x:c r="E4" s="75" t="str">
+        <x:v>retention_percent</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="76" t="str">
+        <x:v>sit</x:v>
+      </x:c>
+      <x:c r="B5" s="76" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C5" s="76" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D5" s="76" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E5" s="78" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="76" t="str">
+        <x:v>stand</x:v>
+      </x:c>
+      <x:c r="B6" s="76" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C6" s="76" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D6" s="76" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="78" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="76" t="str">
+        <x:v>cycle_low</x:v>
+      </x:c>
+      <x:c r="B7" s="76" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C7" s="76" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D7" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="78" t="n">
+        <x:v>93.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="76" t="str">
+        <x:v>cycle_high</x:v>
+      </x:c>
+      <x:c r="B8" s="76" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C8" s="76" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D8" s="76" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E8" s="78" t="n">
+        <x:v>87.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="76" t="str">
+        <x:v>run_low</x:v>
+      </x:c>
+      <x:c r="B9" s="76" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C9" s="76" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D9" s="76" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="78" t="n">
+        <x:v>81.25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="76" t="str">
+        <x:v>run_high</x:v>
+      </x:c>
+      <x:c r="B10" s="76" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C10" s="76" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D10" s="76" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E10" s="78" t="n">
+        <x:v>18.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="32" customHeight="1">
+      <x:c r="A13" s="75" t="str">
+        <x:v>flow_stage</x:v>
+      </x:c>
+      <x:c r="B13" s="75" t="str">
+        <x:v>participants</x:v>
+      </x:c>
+      <x:c r="C13" s="75" t="str">
+        <x:v>participant_stages</x:v>
+      </x:c>
+      <x:c r="D13" s="75" t="str">
+        <x:v>reason</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="76" t="str">
+        <x:v>Source participants</x:v>
+      </x:c>
+      <x:c r="B14" s="76" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C14" s="76" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D14" s="76" t="str">
+        <x:v>17 participants x 6 protocol stages</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="76" t="str">
+        <x:v>Participants with resting-HR anchor</x:v>
+      </x:c>
+      <x:c r="B15" s="76" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C15" s="76" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D15" s="76" t="str">
+        <x:v>P10 excluded because the sitting anchor was missing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="76" t="str">
+        <x:v>Final construct-analysis sample</x:v>
+      </x:c>
+      <x:c r="B16" s="76" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C16" s="76" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D16" s="76" t="str">
+        <x:v>19 additional participant-stage records failed reference HR or VO2 coverage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="34" customHeight="1">
+      <x:c r="A18" s="81" t="str">
+        <x:v>Source files: external_validation/results/reviewer_round5_weee_stage_flow.csv and reviewer_round5_weee_participant_flow.csv</x:v>
+      </x:c>
+      <x:c r="B18" s="81" t="str">
+        <x:v>Source files: external_validation/results/reviewer_round5_weee_stage_flow.csv and reviewer_round5_weee_participant_flow.csv</x:v>
+      </x:c>
+      <x:c r="C18" s="81" t="str">
+        <x:v>Source files: external_validation/results/reviewer_round5_weee_stage_flow.csv and reviewer_round5_weee_participant_flow.csv</x:v>
+      </x:c>
+      <x:c r="D18" s="81" t="str">
+        <x:v>Source files: external_validation/results/reviewer_round5_weee_stage_flow.csv and reviewer_round5_weee_participant_flow.csv</x:v>
+      </x:c>
+      <x:c r="E18" s="81" t="str">
+        <x:v>Source files: external_validation/results/reviewer_round5_weee_stage_flow.csv and reviewer_round5_weee_participant_flow.csv</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A18:E18"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
